--- a/docs/DataModelReview/files/WFDDataModelReview_StateOfPlay.xlsx
+++ b/docs/DataModelReview/files/WFDDataModelReview_StateOfPlay.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nerym\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\WISE.WFD.Documentation\docs\DataModelReview\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C66CBA67-6BCB-4148-B3E2-D199F3AB0B47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7736A9D-5123-4693-8EB0-D016A28DCEC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13695" activeTab="1" xr2:uid="{94644DE7-FCED-4B8C-B8D4-AA0DEEA3D8B7}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13695" xr2:uid="{94644DE7-FCED-4B8C-B8D4-AA0DEEA3D8B7}"/>
   </bookViews>
   <sheets>
     <sheet name="STATUS" sheetId="5" r:id="rId1"/>
@@ -18,7 +18,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="29" r:id="rId3"/>
+    <pivotCache cacheId="5" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -792,392 +792,59 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal_FULL LIST" xfId="2" xr:uid="{72E628DD-073C-4E6F-AF2B-995C240123E7}"/>
     <cellStyle name="Normal_Sheet2" xfId="1" xr:uid="{3F73ABA6-D098-4144-948D-2D6441848EA8}"/>
   </cellStyles>
-  <dxfs count="65">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="2" tint="-9.9978637043366805E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="2" tint="-9.9978637043366805E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="2" tint="-9.9978637043366805E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="2" tint="-9.9978637043366805E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="2" tint="-9.9978637043366805E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="2" tint="-9.9978637043366805E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="2" tint="-9.9978637043366805E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="2" tint="-9.9978637043366805E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="2" tint="-9.9978637043366805E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="2" tint="-9.9978637043366805E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="2" tint="-9.9978637043366805E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="2" tint="-9.9978637043366805E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="2" tint="-9.9978637043366805E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="2" tint="-9.9978637043366805E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="2" tint="-9.9978637043366805E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="2" tint="-9.9978637043366805E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="2" tint="-9.9978637043366805E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="2" tint="-9.9978637043366805E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="2" tint="-9.9978637043366805E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="2" tint="-9.9978637043366805E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="2" tint="-9.9978637043366805E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="2" tint="-9.9978637043366805E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="2" tint="-9.9978637043366805E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="2" tint="-9.9978637043366805E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="2" tint="-9.9978637043366805E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="2" tint="-9.9978637043366805E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="2" tint="-9.9978637043366805E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="2" tint="-9.9978637043366805E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="2" tint="-9.9978637043366805E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="2" tint="-9.9978637043366805E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="2" tint="-9.9978637043366805E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="2" tint="-9.9978637043366805E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="2" tint="-9.9978637043366805E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="2" tint="-9.9978637043366805E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="2" tint="-9.9978637043366805E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="2" tint="-9.9978637043366805E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="2" tint="-9.9978637043366805E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="2" tint="-9.9978637043366805E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="2" tint="-9.9978637043366805E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="2" tint="-9.9978637043366805E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="2" tint="-9.9978637043366805E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="2" tint="-9.9978637043366805E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="2" tint="-9.9978637043366805E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="2" tint="-9.9978637043366805E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="2" tint="-9.9978637043366805E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="2" tint="-9.9978637043366805E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="2" tint="-9.9978637043366805E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="18">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1318,7 +985,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Fernanda Nery" refreshedDate="46173.827506250003" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="180" xr:uid="{83B6D9EE-6618-4074-8602-B9A7EA2DAFEC}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Fernanda Nery" refreshedDate="46174.052605902776" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="180" xr:uid="{83B6D9EE-6618-4074-8602-B9A7EA2DAFEC}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:D1048576" sheet="FULL LIST"/>
   </cacheSource>
@@ -1328,29 +995,29 @@
     </cacheField>
     <cacheField name="section" numFmtId="0">
       <sharedItems containsBlank="1" count="15">
+        <s v="8. Surface water bodies"/>
+        <s v="8.1 Surface water methodologies"/>
+        <s v="metadataAndDocuments"/>
         <s v="1. RBD and competent authorities"/>
         <s v="2.1 RBMP"/>
         <s v="2.2 Measures"/>
         <s v="2.3 Inventory of emissions"/>
         <s v="2.4 Water quantity"/>
         <s v="3. Economic analysis"/>
-        <s v="4. Protected areas"/>
         <s v="5. Exemptions"/>
         <s v="6. Monitoring"/>
         <s v="7. Groundwater bodies"/>
         <s v="7.1 Groundwater methodologies"/>
-        <s v="8. Surface water bodies"/>
-        <s v="8.1 Surface water methodologies"/>
-        <s v="metadataAndDocuments"/>
+        <s v="4. Protected areas"/>
         <m/>
       </sharedItems>
     </cacheField>
     <cacheField name="status" numFmtId="0">
       <sharedItems containsBlank="1" count="5">
+        <s v="«pending»"/>
+        <s v="notApplicable"/>
         <s v="removed"/>
         <s v="revised"/>
-        <s v="«pending»"/>
-        <s v="notApplicable"/>
         <m/>
       </sharedItems>
     </cacheField>
@@ -1369,1072 +1036,1072 @@
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="180">
   <r>
-    <s v="CompetentAuthority_mainRole"/>
+    <s v="FailingRBSP"/>
     <x v="0"/>
     <x v="0"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDRiverBasinDistrictsAndCompetentAuthorities.html"/>
-  </r>
-  <r>
-    <s v="CompetentAuthority_otherRole"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDSurfaceWaterBody.html"/>
+  </r>
+  <r>
+    <s v="QualityElement"/>
     <x v="0"/>
     <x v="0"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDRiverBasinDistrictsAndCompetentAuthorities.html"/>
-  </r>
-  <r>
-    <s v="RBD_euSubUnitCode"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDSurfaceWaterBody.html"/>
+  </r>
+  <r>
+    <s v="QualityElement_qeGrouping"/>
     <x v="0"/>
     <x v="0"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDRiverBasinDistrictsAndCompetentAuthorities.html"/>
-  </r>
-  <r>
-    <s v="RBD_otherCompetentAuthority"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDSurfaceWaterBody.html"/>
+  </r>
+  <r>
+    <s v="SurfaceWaterBody"/>
     <x v="0"/>
     <x v="0"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDRiverBasinDistrictsAndCompetentAuthorities.html"/>
-  </r>
-  <r>
-    <s v="RBD_primeCompetentAuthority"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDSurfaceWaterBody.html"/>
+  </r>
+  <r>
+    <s v="SurfaceWaterBody_hmwbPhysicalAlteration"/>
     <x v="0"/>
     <x v="0"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDRiverBasinDistrictsAndCompetentAuthorities.html"/>
-  </r>
-  <r>
-    <s v="CompetentAuthority"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDSurfaceWaterBody.html"/>
+  </r>
+  <r>
+    <s v="SurfaceWaterBody_hmwbWaterUse"/>
     <x v="0"/>
-    <x v="1"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDRiverBasinDistrictsAndCompetentAuthorities.html"/>
-  </r>
-  <r>
-    <s v="RBD"/>
-    <x v="0"/>
-    <x v="1"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDRiverBasinDistrictsAndCompetentAuthorities.html"/>
-  </r>
-  <r>
-    <s v="RBDSUCA"/>
-    <x v="0"/>
-    <x v="1"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDRiverBasinDistrictsAndCompetentAuthorities.html"/>
-  </r>
-  <r>
-    <s v="RBMPPoM"/>
-    <x v="1"/>
-    <x v="0"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDMeasures.html"/>
-  </r>
-  <r>
-    <s v="CoOrd"/>
-    <x v="1"/>
-    <x v="1"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDMeasures.html"/>
-  </r>
-  <r>
-    <s v="RBMP"/>
-    <x v="1"/>
-    <x v="1"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDMeasures.html"/>
-  </r>
-  <r>
-    <s v="RBMP_documentProvision"/>
-    <x v="1"/>
-    <x v="1"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDMeasures.html"/>
-  </r>
-  <r>
-    <s v="RBMP_impactPublicParticipation"/>
-    <x v="1"/>
-    <x v="1"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDMeasures.html"/>
-  </r>
-  <r>
-    <s v="RBMP_ongoingStakeholderInvolvement"/>
-    <x v="1"/>
-    <x v="1"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDMeasures.html"/>
-  </r>
-  <r>
-    <s v="RBMP_publicConsultationInformation"/>
-    <x v="1"/>
-    <x v="1"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDMeasures.html"/>
-  </r>
-  <r>
-    <s v="RBMP_rbmpConsultation"/>
-    <x v="1"/>
-    <x v="1"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDMeasures.html"/>
-  </r>
-  <r>
-    <s v="RBMP_stakeholderGroups"/>
-    <x v="1"/>
-    <x v="1"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDMeasures.html"/>
-  </r>
-  <r>
-    <s v="RBMP_subPlansCoverage"/>
-    <x v="1"/>
-    <x v="1"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDMeasures.html"/>
-  </r>
-  <r>
-    <s v="TargetedQ"/>
-    <x v="1"/>
-    <x v="1"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDMeasures.html"/>
-  </r>
-  <r>
-    <s v="TargetedQ_basicMeasuresArt113hIssues"/>
-    <x v="1"/>
-    <x v="1"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDMeasures.html"/>
-  </r>
-  <r>
-    <s v="TargetedQ_climateChangeAspectsConsidered"/>
-    <x v="1"/>
-    <x v="1"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDMeasures.html"/>
-  </r>
-  <r>
-    <s v="TargetedQ_msfdMeasuresNeeded"/>
-    <x v="1"/>
-    <x v="1"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDMeasures.html"/>
-  </r>
-  <r>
-    <s v="IndicatorGap"/>
-    <x v="2"/>
-    <x v="0"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDMeasures.html"/>
-  </r>
-  <r>
-    <s v="KeyTypeMeasureIndicator"/>
-    <x v="2"/>
-    <x v="0"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDMeasures.html"/>
-  </r>
-  <r>
-    <s v="KTM"/>
-    <x v="2"/>
-    <x v="0"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDMeasures.html"/>
-  </r>
-  <r>
-    <s v="Measure_basicMeasureType"/>
-    <x v="2"/>
-    <x v="0"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDMeasures.html"/>
-  </r>
-  <r>
-    <s v="PoM"/>
-    <x v="2"/>
-    <x v="0"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDMeasures.html"/>
-  </r>
-  <r>
-    <s v="SignificantPressureSubstanceFailing"/>
-    <x v="2"/>
-    <x v="0"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDMeasures.html"/>
-  </r>
-  <r>
-    <s v="Costs"/>
-    <x v="2"/>
-    <x v="1"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDMeasures.html"/>
-  </r>
-  <r>
-    <s v="Measure"/>
-    <x v="2"/>
-    <x v="1"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDMeasures.html"/>
-  </r>
-  <r>
-    <s v="Progress"/>
-    <x v="2"/>
-    <x v="1"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDMeasures.html"/>
-  </r>
-  <r>
-    <s v="InputCategory"/>
-    <x v="3"/>
-    <x v="0"/>
-    <s v="WISE-1"/>
-  </r>
-  <r>
-    <s v="InputInventory"/>
-    <x v="3"/>
-    <x v="0"/>
-    <s v="WISE-1"/>
-  </r>
-  <r>
-    <s v="InputPollutant"/>
-    <x v="3"/>
-    <x v="0"/>
-    <s v="WISE-1"/>
-  </r>
-  <r>
-    <s v="InputTotal"/>
-    <x v="3"/>
-    <x v="0"/>
-    <s v="WISE-1"/>
-  </r>
-  <r>
-    <s v="InputTrend"/>
-    <x v="3"/>
-    <x v="0"/>
-    <s v="WISE-1"/>
-  </r>
-  <r>
-    <s v="WaterQuantity"/>
-    <x v="4"/>
-    <x v="0"/>
-    <s v="WISE-3"/>
-  </r>
-  <r>
-    <s v="WQUse"/>
-    <x v="4"/>
-    <x v="0"/>
-    <s v="WISE-3"/>
-  </r>
-  <r>
-    <s v="Service_serviceWaterUseOther"/>
-    <x v="5"/>
-    <x v="0"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDEconomicAnalysis.html"/>
-  </r>
-  <r>
-    <s v="EconomicAnalysis"/>
-    <x v="5"/>
-    <x v="1"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDEconomicAnalysis.html"/>
-  </r>
-  <r>
-    <s v="Service"/>
-    <x v="5"/>
-    <x v="1"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDEconomicAnalysis.html"/>
-  </r>
-  <r>
-    <s v="GWAssociatedProtectedArea"/>
-    <x v="6"/>
-    <x v="1"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDProtectedAreas.html"/>
-  </r>
-  <r>
-    <s v="SWAssociatedProtectedArea"/>
-    <x v="6"/>
-    <x v="1"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDProtectedAreas.html"/>
-  </r>
-  <r>
-    <s v="GWExemptions"/>
-    <x v="7"/>
-    <x v="0"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDExemptions.html"/>
-  </r>
-  <r>
-    <s v="GWExemptions_gwDisproportionateCostAlternativeFinancing"/>
-    <x v="7"/>
-    <x v="0"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDExemptions.html"/>
-  </r>
-  <r>
-    <s v="GWExemptions_gwDisproportionateCostAnalysis"/>
-    <x v="7"/>
-    <x v="0"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDExemptions.html"/>
-  </r>
-  <r>
-    <s v="GWExemptions_gwDisproportionateCostScale"/>
-    <x v="7"/>
-    <x v="0"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDExemptions.html"/>
-  </r>
-  <r>
-    <s v="GWExemptions_gwExemption44Driver"/>
-    <x v="7"/>
-    <x v="0"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDExemptions.html"/>
-  </r>
-  <r>
-    <s v="GWExemptions_gwExemption44Impact"/>
-    <x v="7"/>
-    <x v="0"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDExemptions.html"/>
-  </r>
-  <r>
-    <s v="GWExemptions_gwExemption45Driver"/>
-    <x v="7"/>
-    <x v="0"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDExemptions.html"/>
-  </r>
-  <r>
-    <s v="GWExemptions_gwExemption45Impact"/>
-    <x v="7"/>
-    <x v="0"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDExemptions.html"/>
-  </r>
-  <r>
-    <s v="GWExemptions_gwExemption46"/>
-    <x v="7"/>
-    <x v="0"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDExemptions.html"/>
-  </r>
-  <r>
-    <s v="GWExemptions_gwExemption47"/>
-    <x v="7"/>
-    <x v="0"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDExemptions.html"/>
-  </r>
-  <r>
-    <s v="GWExemptions_gwNaturalConditions"/>
-    <x v="7"/>
-    <x v="0"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDExemptions.html"/>
-  </r>
-  <r>
-    <s v="GWExemptions_gwTechnicalInfeasibility"/>
-    <x v="7"/>
-    <x v="0"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDExemptions.html"/>
-  </r>
-  <r>
-    <s v="SWExemptions"/>
-    <x v="7"/>
-    <x v="0"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDExemptions.html"/>
-  </r>
-  <r>
-    <s v="SWExemptions_swDisproportionateCostAlternativeFinancing"/>
-    <x v="7"/>
-    <x v="0"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDExemptions.html"/>
-  </r>
-  <r>
-    <s v="SWExemptions_swDisproportionateCostAnalysis"/>
-    <x v="7"/>
-    <x v="0"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDExemptions.html"/>
-  </r>
-  <r>
-    <s v="SWExemptions_swDisproportionateCostScale"/>
-    <x v="7"/>
-    <x v="0"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDExemptions.html"/>
-  </r>
-  <r>
-    <s v="SWExemptions_swExemption44Driver"/>
-    <x v="7"/>
-    <x v="0"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDExemptions.html"/>
-  </r>
-  <r>
-    <s v="SWExemptions_swExemption44Impact"/>
-    <x v="7"/>
-    <x v="0"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDExemptions.html"/>
-  </r>
-  <r>
-    <s v="SWExemptions_swExemption45Driver"/>
-    <x v="7"/>
-    <x v="0"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDExemptions.html"/>
-  </r>
-  <r>
-    <s v="SWExemptions_swExemption45Impact"/>
-    <x v="7"/>
-    <x v="0"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDExemptions.html"/>
-  </r>
-  <r>
-    <s v="SWExemptions_swExemption46"/>
-    <x v="7"/>
-    <x v="0"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDExemptions.html"/>
-  </r>
-  <r>
-    <s v="SWExemptions_swExemption47"/>
-    <x v="7"/>
-    <x v="0"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDExemptions.html"/>
-  </r>
-  <r>
-    <s v="SWExemptions_swNaturalConditions"/>
-    <x v="7"/>
-    <x v="0"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDExemptions.html"/>
-  </r>
-  <r>
-    <s v="SWExemptions_swTechnicalInfeasibility"/>
-    <x v="7"/>
-    <x v="0"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDExemptions.html"/>
-  </r>
-  <r>
-    <s v="GWAssociatedProtectedArea_protectedAreaExemption"/>
-    <x v="7"/>
-    <x v="1"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDEconomicAnalysis.html"/>
-  </r>
-  <r>
-    <s v="GWChemicalExemptionType"/>
-    <x v="7"/>
-    <x v="1"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDEconomicAnalysis.html"/>
-  </r>
-  <r>
-    <s v="QualityElement_qeEcologicalExemptionType"/>
-    <x v="7"/>
-    <x v="1"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDEconomicAnalysis.html"/>
-  </r>
-  <r>
-    <s v="SWAssociatedProtectedArea_protectedAreaExemption"/>
-    <x v="7"/>
-    <x v="1"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDEconomicAnalysis.html"/>
-  </r>
-  <r>
-    <s v="SWChemicalExemptionType"/>
-    <x v="7"/>
-    <x v="1"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDEconomicAnalysis.html"/>
-  </r>
-  <r>
-    <s v="SWEcologicalExemptionType"/>
-    <x v="7"/>
-    <x v="1"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDEconomicAnalysis.html"/>
-  </r>
-  <r>
-    <s v="Monitoring"/>
-    <x v="8"/>
-    <x v="0"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDMonitoring.html"/>
-  </r>
-  <r>
-    <s v="MonitoringSite_euProgrammeCode"/>
-    <x v="8"/>
-    <x v="0"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDMonitoring.html"/>
-  </r>
-  <r>
-    <s v="Programme"/>
-    <x v="8"/>
-    <x v="0"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDMonitoring.html"/>
-  </r>
-  <r>
-    <s v="ChemicalEcologicalQuantitativeMonitoring"/>
-    <x v="8"/>
-    <x v="1"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDMonitoring.html"/>
-  </r>
-  <r>
-    <s v="MonitoringSite"/>
-    <x v="8"/>
-    <x v="1"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDMonitoring.html"/>
-  </r>
-  <r>
-    <s v="GWB"/>
-    <x v="9"/>
-    <x v="0"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDGroundWaterBody.html"/>
-  </r>
-  <r>
-    <s v="GroundWaterBody"/>
-    <x v="9"/>
-    <x v="1"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDGroundWaterBody.html"/>
-  </r>
-  <r>
-    <s v="GroundWaterBody_gwChemicalReasonsForFailure"/>
-    <x v="9"/>
-    <x v="1"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDGroundWaterBody.html"/>
-  </r>
-  <r>
-    <s v="GroundWaterBody_gwQuantitativeExemptionPressure"/>
-    <x v="7"/>
-    <x v="0"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDExemptions.html"/>
-  </r>
-  <r>
-    <s v="GroundWaterBody_gwQuantitativeExemptionType"/>
-    <x v="7"/>
-    <x v="1"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDExemptions.html"/>
-  </r>
-  <r>
-    <s v="GroundWaterBody_gwQuantitativeReasonsForFailure"/>
-    <x v="9"/>
-    <x v="1"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDGroundWaterBody.html"/>
-  </r>
-  <r>
-    <s v="GroundWaterBody_gwReasonsForRiskQuantitative"/>
-    <x v="9"/>
-    <x v="0"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDGroundWaterBody.html"/>
-  </r>
-  <r>
-    <s v="GroundWaterBody_gwSignificantImpactType"/>
-    <x v="9"/>
-    <x v="1"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDGroundWaterBody.html"/>
-  </r>
-  <r>
-    <s v="GroundWaterBody_gwSignificantPressureType"/>
-    <x v="9"/>
-    <x v="1"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDGroundWaterBody.html"/>
-  </r>
-  <r>
-    <s v="GroundWaterBody_linkSurfaceWaterBodyCode"/>
-    <x v="9"/>
-    <x v="1"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDGroundWaterBody.html"/>
-  </r>
-  <r>
-    <s v="GWPollutant"/>
-    <x v="9"/>
-    <x v="1"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDGroundWaterBody.html"/>
-  </r>
-  <r>
-    <s v="ThresholdValue"/>
-    <x v="10"/>
-    <x v="2"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDGroundwaterMethodologies.html"/>
-  </r>
-  <r>
-    <s v="GWMET"/>
-    <x v="10"/>
-    <x v="0"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDGroundwaterMethodologies.html"/>
-  </r>
-  <r>
-    <s v="GWPressures_gwPressuresNotAssessed"/>
-    <x v="10"/>
-    <x v="0"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDGroundwaterMethodologies.html"/>
-  </r>
-  <r>
-    <s v="GWMethodologies"/>
-    <x v="10"/>
-    <x v="1"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDGroundwaterMethodologies.html"/>
-  </r>
-  <r>
-    <s v="GWPressures"/>
-    <x v="10"/>
-    <x v="1"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDGroundwaterMethodologies.html"/>
-  </r>
-  <r>
-    <s v="FailingRBSP"/>
-    <x v="11"/>
-    <x v="2"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDSurfaceWaterBody.html"/>
-  </r>
-  <r>
-    <s v="QualityElement"/>
-    <x v="11"/>
-    <x v="2"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDSurfaceWaterBody.html"/>
-  </r>
-  <r>
-    <s v="QualityElement_qeGrouping"/>
-    <x v="11"/>
-    <x v="2"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDSurfaceWaterBody.html"/>
-  </r>
-  <r>
-    <s v="SurfaceWaterBody"/>
-    <x v="11"/>
-    <x v="2"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDSurfaceWaterBody.html"/>
-  </r>
-  <r>
-    <s v="SurfaceWaterBody_hmwbPhysicalAlteration"/>
-    <x v="11"/>
-    <x v="2"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDSurfaceWaterBody.html"/>
-  </r>
-  <r>
-    <s v="SurfaceWaterBody_hmwbWaterUse"/>
-    <x v="11"/>
-    <x v="2"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDSurfaceWaterBody.html"/>
-  </r>
-  <r>
-    <s v="SurfaceWaterBody_surfaceWaterBodyIntercalibrationType"/>
-    <x v="11"/>
-    <x v="2"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDSurfaceWaterBody.html"/>
-  </r>
-  <r>
-    <s v="SurfaceWaterBody_swChemicalStatusGrouping"/>
-    <x v="11"/>
-    <x v="2"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDSurfaceWaterBody.html"/>
-  </r>
-  <r>
-    <s v="SurfaceWaterBody_swSignificantImpactType"/>
-    <x v="11"/>
-    <x v="2"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDSurfaceWaterBody.html"/>
-  </r>
-  <r>
-    <s v="SurfaceWaterBody_swSignificantPressureType"/>
-    <x v="11"/>
-    <x v="2"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDSurfaceWaterBody.html"/>
-  </r>
-  <r>
-    <s v="SWB_SWPrioritySubstance"/>
-    <x v="11"/>
-    <x v="2"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDSurfaceWaterBody.html"/>
-  </r>
-  <r>
-    <s v="SWB"/>
-    <x v="11"/>
     <x v="0"/>
     <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDSurfaceWaterBody.html"/>
   </r>
   <r>
+    <s v="SurfaceWaterBody_surfaceWaterBodyIntercalibrationType"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDSurfaceWaterBody.html"/>
+  </r>
+  <r>
+    <s v="SurfaceWaterBody_swChemicalStatusGrouping"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDSurfaceWaterBody.html"/>
+  </r>
+  <r>
+    <s v="SurfaceWaterBody_swSignificantImpactType"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDSurfaceWaterBody.html"/>
+  </r>
+  <r>
+    <s v="SurfaceWaterBody_swSignificantPressureType"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDSurfaceWaterBody.html"/>
+  </r>
+  <r>
+    <s v="SWB_SWPrioritySubstance"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDSurfaceWaterBody.html"/>
+  </r>
+  <r>
     <s v="BQEMethod"/>
-    <x v="12"/>
-    <x v="2"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDSurfaceWaterMethodologies.html"/>
-  </r>
-  <r>
-    <s v="BQEMethod_bqeSensitivityImpactOther"/>
-    <x v="12"/>
-    <x v="2"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDSurfaceWaterMethodologies.html"/>
-  </r>
-  <r>
-    <s v="SWMET_SWPrioritySubstance"/>
-    <x v="12"/>
-    <x v="2"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDSurfaceWaterMethodologies.html"/>
-  </r>
-  <r>
-    <s v="SWPhysicoChemicalQE"/>
-    <x v="12"/>
-    <x v="2"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDSurfaceWaterMethodologies.html"/>
-  </r>
-  <r>
-    <s v="SWPhysicoChemicalQE_physChemTypeCode"/>
-    <x v="12"/>
-    <x v="2"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDSurfaceWaterMethodologies.html"/>
-  </r>
-  <r>
-    <s v="SWPrioritySubstance_swPrioritySubstanceExceedanceType"/>
-    <x v="12"/>
-    <x v="2"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDSurfaceWaterMethodologies.html"/>
-  </r>
-  <r>
-    <s v="SWRBSP"/>
-    <x v="12"/>
-    <x v="2"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDSurfaceWaterMethodologies.html"/>
-  </r>
-  <r>
-    <s v="SWSupportingQE"/>
-    <x v="12"/>
-    <x v="2"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDSurfaceWaterMethodologies.html"/>
-  </r>
-  <r>
-    <s v="SWType"/>
-    <x v="12"/>
-    <x v="2"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDSurfaceWaterMethodologies.html"/>
-  </r>
-  <r>
-    <s v="SWType_swIntercalibrationType"/>
-    <x v="12"/>
-    <x v="2"/>
-    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDSurfaceWaterMethodologies.html"/>
-  </r>
-  <r>
-    <s v="SWMET"/>
-    <x v="12"/>
+    <x v="1"/>
     <x v="0"/>
     <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDSurfaceWaterMethodologies.html"/>
   </r>
   <r>
-    <s v="SWPressures_swPressuresNotAssessed"/>
-    <x v="12"/>
+    <s v="BQEMethod_bqeSensitivityImpactOther"/>
+    <x v="1"/>
     <x v="0"/>
     <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDSurfaceWaterMethodologies.html"/>
   </r>
   <r>
+    <s v="SWMET_SWPrioritySubstance"/>
+    <x v="1"/>
+    <x v="0"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDSurfaceWaterMethodologies.html"/>
+  </r>
+  <r>
+    <s v="SWPhysicoChemicalQE"/>
+    <x v="1"/>
+    <x v="0"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDSurfaceWaterMethodologies.html"/>
+  </r>
+  <r>
+    <s v="SWPhysicoChemicalQE_physChemTypeCode"/>
+    <x v="1"/>
+    <x v="0"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDSurfaceWaterMethodologies.html"/>
+  </r>
+  <r>
+    <s v="SWPrioritySubstance_swPrioritySubstanceExceedanceType"/>
+    <x v="1"/>
+    <x v="0"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDSurfaceWaterMethodologies.html"/>
+  </r>
+  <r>
+    <s v="SWRBSP"/>
+    <x v="1"/>
+    <x v="0"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDSurfaceWaterMethodologies.html"/>
+  </r>
+  <r>
+    <s v="SWSupportingQE"/>
+    <x v="1"/>
+    <x v="0"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDSurfaceWaterMethodologies.html"/>
+  </r>
+  <r>
+    <s v="SWType"/>
+    <x v="1"/>
+    <x v="0"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDSurfaceWaterMethodologies.html"/>
+  </r>
+  <r>
+    <s v="SWType_swIntercalibrationType"/>
+    <x v="1"/>
+    <x v="0"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDSurfaceWaterMethodologies.html"/>
+  </r>
+  <r>
+    <s v="CoOrd_iRBMPReference"/>
+    <x v="2"/>
+    <x v="1"/>
+    <m/>
+  </r>
+  <r>
+    <s v="Costs_costExplanation20152021Reference"/>
+    <x v="2"/>
+    <x v="1"/>
+    <m/>
+  </r>
+  <r>
+    <s v="Costs_costExplanation20212027Reference"/>
+    <x v="2"/>
+    <x v="1"/>
+    <m/>
+  </r>
+  <r>
+    <s v="dcMetadata"/>
+    <x v="2"/>
+    <x v="1"/>
+    <m/>
+  </r>
+  <r>
+    <s v="EconomicAnalysis_article94Reference"/>
+    <x v="2"/>
+    <x v="1"/>
+    <m/>
+  </r>
+  <r>
+    <s v="EconomicAnalysis_costEffectivenessReference"/>
+    <x v="2"/>
+    <x v="1"/>
+    <m/>
+  </r>
+  <r>
+    <s v="EconomicAnalysis_costRecoveryReference"/>
+    <x v="2"/>
+    <x v="1"/>
+    <m/>
+  </r>
+  <r>
+    <s v="EconomicAnalysis_economicAnalysisReference"/>
+    <x v="2"/>
+    <x v="1"/>
+    <m/>
+  </r>
+  <r>
+    <s v="GWExemptions_driversGWExemptionsReference"/>
+    <x v="2"/>
+    <x v="1"/>
+    <m/>
+  </r>
+  <r>
+    <s v="GWExemptions_gwExemptionsReference"/>
+    <x v="2"/>
+    <x v="1"/>
+    <m/>
+  </r>
+  <r>
+    <s v="GWMethodologies_gwCharacterisationReference"/>
+    <x v="2"/>
+    <x v="1"/>
+    <m/>
+  </r>
+  <r>
+    <s v="GWMethodologies_gwMethodologiesChemicalClassificationReference"/>
+    <x v="2"/>
+    <x v="1"/>
+    <m/>
+  </r>
+  <r>
+    <s v="GWMethodologies_gwMethodologiesTransboundaryReference"/>
+    <x v="2"/>
+    <x v="1"/>
+    <m/>
+  </r>
+  <r>
+    <s v="GWMethodologies_gwMethQuantitativeClassificationReference"/>
+    <x v="2"/>
+    <x v="1"/>
+    <m/>
+  </r>
+  <r>
+    <s v="GWPressures_gwPressuresReference"/>
+    <x v="2"/>
+    <x v="1"/>
+    <m/>
+  </r>
+  <r>
+    <s v="InputInventory_inputInventoryReference"/>
+    <x v="2"/>
+    <x v="1"/>
+    <m/>
+  </r>
+  <r>
+    <s v="InputPollutant_inputMethodReference"/>
+    <x v="2"/>
+    <x v="1"/>
+    <m/>
+  </r>
+  <r>
+    <s v="Measure_measureReference"/>
+    <x v="2"/>
+    <x v="1"/>
+    <m/>
+  </r>
+  <r>
+    <s v="Metadata"/>
+    <x v="2"/>
+    <x v="1"/>
+    <m/>
+  </r>
+  <r>
+    <s v="Programme_programmeReference"/>
+    <x v="2"/>
+    <x v="1"/>
+    <m/>
+  </r>
+  <r>
+    <s v="Progress_measuresFromPreviousProgrammeReference"/>
+    <x v="2"/>
+    <x v="1"/>
+    <m/>
+  </r>
+  <r>
+    <s v="RBMP_consultationResponsesReference"/>
+    <x v="2"/>
+    <x v="1"/>
+    <m/>
+  </r>
+  <r>
+    <s v="RBMP_fdCoordinationReference"/>
+    <x v="2"/>
+    <x v="1"/>
+    <m/>
+  </r>
+  <r>
+    <s v="RBMP_msfdCoordinationReference"/>
+    <x v="2"/>
+    <x v="1"/>
+    <m/>
+  </r>
+  <r>
+    <s v="RBMP_publicParticipationReference"/>
+    <x v="2"/>
+    <x v="1"/>
+    <m/>
+  </r>
+  <r>
+    <s v="RBMP_seaReference"/>
+    <x v="2"/>
+    <x v="1"/>
+    <m/>
+  </r>
+  <r>
+    <s v="RBMP_subPlansReference"/>
+    <x v="2"/>
+    <x v="1"/>
+    <m/>
+  </r>
+  <r>
+    <s v="ReferenceType"/>
+    <x v="2"/>
+    <x v="1"/>
+    <m/>
+  </r>
+  <r>
+    <s v="Service_serviceCostInstrumentReference"/>
+    <x v="2"/>
+    <x v="1"/>
+    <m/>
+  </r>
+  <r>
+    <s v="SWChemicalStatusClassificationRBD_bioavailabilityReference"/>
+    <x v="2"/>
+    <x v="1"/>
+    <m/>
+  </r>
+  <r>
+    <s v="SWChemicalStatusClassificationRBD_chemicalStatusReference"/>
+    <x v="2"/>
+    <x v="1"/>
+    <m/>
+  </r>
+  <r>
+    <s v="SWChemicalStatusClassificationRBD_longTermTrendAnalysisReference"/>
+    <x v="2"/>
+    <x v="1"/>
+    <m/>
+  </r>
+  <r>
+    <s v="SWChemStClassRBD_alternativeMixingZoneMethodologyReference"/>
+    <x v="2"/>
+    <x v="1"/>
+    <m/>
+  </r>
+  <r>
+    <s v="SWChemStClassRBD_approachSWBNotMonitoredChemicalReference"/>
+    <x v="2"/>
+    <x v="1"/>
+    <m/>
+  </r>
+  <r>
+    <s v="SWChemStClassRBD_backgroundConcentrationsReference"/>
+    <x v="2"/>
+    <x v="1"/>
+    <m/>
+  </r>
+  <r>
+    <s v="SWChemStClassRBD_mixingZoneMeasuresReductionReference"/>
+    <x v="2"/>
+    <x v="1"/>
+    <m/>
+  </r>
+  <r>
+    <s v="SWExemptions_driversSWExemptionsReference"/>
+    <x v="2"/>
+    <x v="1"/>
+    <m/>
+  </r>
+  <r>
+    <s v="SWExemptions_swExemptionsReference"/>
+    <x v="2"/>
+    <x v="1"/>
+    <m/>
+  </r>
+  <r>
+    <s v="SWManagementObjectives_managementObjectivesReference"/>
+    <x v="2"/>
+    <x v="1"/>
+    <m/>
+  </r>
+  <r>
+    <s v="SWManagementObjectives_waterResourcePlansReference"/>
+    <x v="2"/>
+    <x v="1"/>
+    <m/>
+  </r>
+  <r>
+    <s v="SWMethodologies_hmwbMethodologyReference"/>
+    <x v="2"/>
+    <x v="1"/>
+    <m/>
+  </r>
+  <r>
+    <s v="SWMethodologies_iRBDTypologyCoOrdinationReference"/>
+    <x v="2"/>
+    <x v="1"/>
+    <m/>
+  </r>
+  <r>
+    <s v="SWMethodologies_smallWBsMethodologyReference"/>
+    <x v="2"/>
+    <x v="1"/>
+    <m/>
+  </r>
+  <r>
+    <s v="SWMethodologies_typologyMethodologyReference"/>
+    <x v="2"/>
+    <x v="1"/>
+    <m/>
+  </r>
+  <r>
+    <s v="SWPressures_swPressuresReference"/>
+    <x v="2"/>
+    <x v="1"/>
+    <m/>
+  </r>
+  <r>
+    <s v="SWTargetedQ_driversFailureEcologicalStatusPotentialReference"/>
+    <x v="2"/>
+    <x v="1"/>
+    <m/>
+  </r>
+  <r>
+    <s v="SWTargetedQ_ecologicalStatusMethodReference"/>
+    <x v="2"/>
+    <x v="1"/>
+    <m/>
+  </r>
+  <r>
+    <s v="SWTargetedQ_gepMethodReference"/>
+    <x v="2"/>
+    <x v="1"/>
+    <m/>
+  </r>
+  <r>
+    <s v="TargetedQ_basicMeasuresArt113b-lReference"/>
+    <x v="2"/>
+    <x v="1"/>
+    <m/>
+  </r>
+  <r>
+    <s v="TargetedQ_otherAspectsReference"/>
+    <x v="2"/>
+    <x v="1"/>
+    <m/>
+  </r>
+  <r>
+    <s v="WaterQuantity_wqAlternativeIndicatorReference"/>
+    <x v="2"/>
+    <x v="1"/>
+    <m/>
+  </r>
+  <r>
+    <s v="WaterQuantity_wqCalculationMethodReference"/>
+    <x v="2"/>
+    <x v="1"/>
+    <m/>
+  </r>
+  <r>
+    <s v="WFDCommon"/>
+    <x v="2"/>
+    <x v="1"/>
+    <m/>
+  </r>
+  <r>
+    <s v="CompetentAuthority_mainRole"/>
+    <x v="3"/>
+    <x v="2"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDRiverBasinDistrictsAndCompetentAuthorities.html"/>
+  </r>
+  <r>
+    <s v="CompetentAuthority_otherRole"/>
+    <x v="3"/>
+    <x v="2"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDRiverBasinDistrictsAndCompetentAuthorities.html"/>
+  </r>
+  <r>
+    <s v="RBD_euSubUnitCode"/>
+    <x v="3"/>
+    <x v="2"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDRiverBasinDistrictsAndCompetentAuthorities.html"/>
+  </r>
+  <r>
+    <s v="RBD_otherCompetentAuthority"/>
+    <x v="3"/>
+    <x v="2"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDRiverBasinDistrictsAndCompetentAuthorities.html"/>
+  </r>
+  <r>
+    <s v="RBD_primeCompetentAuthority"/>
+    <x v="3"/>
+    <x v="2"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDRiverBasinDistrictsAndCompetentAuthorities.html"/>
+  </r>
+  <r>
+    <s v="RBMPPoM"/>
+    <x v="4"/>
+    <x v="2"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDMeasures.html"/>
+  </r>
+  <r>
+    <s v="IndicatorGap"/>
+    <x v="5"/>
+    <x v="2"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDMeasures.html"/>
+  </r>
+  <r>
+    <s v="KeyTypeMeasureIndicator"/>
+    <x v="5"/>
+    <x v="2"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDMeasures.html"/>
+  </r>
+  <r>
+    <s v="KTM"/>
+    <x v="5"/>
+    <x v="2"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDMeasures.html"/>
+  </r>
+  <r>
+    <s v="Measure_basicMeasureType"/>
+    <x v="5"/>
+    <x v="2"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDMeasures.html"/>
+  </r>
+  <r>
+    <s v="PoM"/>
+    <x v="5"/>
+    <x v="2"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDMeasures.html"/>
+  </r>
+  <r>
+    <s v="SignificantPressureSubstanceFailing"/>
+    <x v="5"/>
+    <x v="2"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDMeasures.html"/>
+  </r>
+  <r>
+    <s v="InputCategory"/>
+    <x v="6"/>
+    <x v="2"/>
+    <s v="WISE-1"/>
+  </r>
+  <r>
+    <s v="InputInventory"/>
+    <x v="6"/>
+    <x v="2"/>
+    <s v="WISE-1"/>
+  </r>
+  <r>
+    <s v="InputPollutant"/>
+    <x v="6"/>
+    <x v="2"/>
+    <s v="WISE-1"/>
+  </r>
+  <r>
+    <s v="InputTotal"/>
+    <x v="6"/>
+    <x v="2"/>
+    <s v="WISE-1"/>
+  </r>
+  <r>
+    <s v="InputTrend"/>
+    <x v="6"/>
+    <x v="2"/>
+    <s v="WISE-1"/>
+  </r>
+  <r>
+    <s v="WaterQuantity"/>
+    <x v="7"/>
+    <x v="2"/>
+    <s v="WISE-3"/>
+  </r>
+  <r>
+    <s v="WQUse"/>
+    <x v="7"/>
+    <x v="2"/>
+    <s v="WISE-3"/>
+  </r>
+  <r>
+    <s v="Service_serviceWaterUseOther"/>
+    <x v="8"/>
+    <x v="2"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDEconomicAnalysis.html"/>
+  </r>
+  <r>
+    <s v="GroundWaterBody_gwQuantitativeExemptionPressure"/>
+    <x v="9"/>
+    <x v="2"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDExemptions.html"/>
+  </r>
+  <r>
+    <s v="GWExemptions"/>
+    <x v="9"/>
+    <x v="2"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDExemptions.html"/>
+  </r>
+  <r>
+    <s v="GWExemptions_gwDisproportionateCostAlternativeFinancing"/>
+    <x v="9"/>
+    <x v="2"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDExemptions.html"/>
+  </r>
+  <r>
+    <s v="GWExemptions_gwDisproportionateCostAnalysis"/>
+    <x v="9"/>
+    <x v="2"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDExemptions.html"/>
+  </r>
+  <r>
+    <s v="GWExemptions_gwDisproportionateCostScale"/>
+    <x v="9"/>
+    <x v="2"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDExemptions.html"/>
+  </r>
+  <r>
+    <s v="GWExemptions_gwExemption44Driver"/>
+    <x v="9"/>
+    <x v="2"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDExemptions.html"/>
+  </r>
+  <r>
+    <s v="GWExemptions_gwExemption44Impact"/>
+    <x v="9"/>
+    <x v="2"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDExemptions.html"/>
+  </r>
+  <r>
+    <s v="GWExemptions_gwExemption45Driver"/>
+    <x v="9"/>
+    <x v="2"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDExemptions.html"/>
+  </r>
+  <r>
+    <s v="GWExemptions_gwExemption45Impact"/>
+    <x v="9"/>
+    <x v="2"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDExemptions.html"/>
+  </r>
+  <r>
+    <s v="GWExemptions_gwExemption46"/>
+    <x v="9"/>
+    <x v="2"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDExemptions.html"/>
+  </r>
+  <r>
+    <s v="GWExemptions_gwExemption47"/>
+    <x v="9"/>
+    <x v="2"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDExemptions.html"/>
+  </r>
+  <r>
+    <s v="GWExemptions_gwNaturalConditions"/>
+    <x v="9"/>
+    <x v="2"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDExemptions.html"/>
+  </r>
+  <r>
+    <s v="GWExemptions_gwTechnicalInfeasibility"/>
+    <x v="9"/>
+    <x v="2"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDExemptions.html"/>
+  </r>
+  <r>
+    <s v="SWExemptions"/>
+    <x v="9"/>
+    <x v="2"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDExemptions.html"/>
+  </r>
+  <r>
+    <s v="SWExemptions_swDisproportionateCostAlternativeFinancing"/>
+    <x v="9"/>
+    <x v="2"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDExemptions.html"/>
+  </r>
+  <r>
+    <s v="SWExemptions_swDisproportionateCostAnalysis"/>
+    <x v="9"/>
+    <x v="2"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDExemptions.html"/>
+  </r>
+  <r>
+    <s v="SWExemptions_swDisproportionateCostScale"/>
+    <x v="9"/>
+    <x v="2"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDExemptions.html"/>
+  </r>
+  <r>
+    <s v="SWExemptions_swExemption44Driver"/>
+    <x v="9"/>
+    <x v="2"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDExemptions.html"/>
+  </r>
+  <r>
+    <s v="SWExemptions_swExemption44Impact"/>
+    <x v="9"/>
+    <x v="2"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDExemptions.html"/>
+  </r>
+  <r>
+    <s v="SWExemptions_swExemption45Driver"/>
+    <x v="9"/>
+    <x v="2"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDExemptions.html"/>
+  </r>
+  <r>
+    <s v="SWExemptions_swExemption45Impact"/>
+    <x v="9"/>
+    <x v="2"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDExemptions.html"/>
+  </r>
+  <r>
+    <s v="SWExemptions_swExemption46"/>
+    <x v="9"/>
+    <x v="2"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDExemptions.html"/>
+  </r>
+  <r>
+    <s v="SWExemptions_swExemption47"/>
+    <x v="9"/>
+    <x v="2"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDExemptions.html"/>
+  </r>
+  <r>
+    <s v="SWExemptions_swNaturalConditions"/>
+    <x v="9"/>
+    <x v="2"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDExemptions.html"/>
+  </r>
+  <r>
+    <s v="SWExemptions_swTechnicalInfeasibility"/>
+    <x v="9"/>
+    <x v="2"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDExemptions.html"/>
+  </r>
+  <r>
+    <s v="Monitoring"/>
+    <x v="10"/>
+    <x v="2"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDMonitoring.html"/>
+  </r>
+  <r>
+    <s v="MonitoringSite_euProgrammeCode"/>
+    <x v="10"/>
+    <x v="2"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDMonitoring.html"/>
+  </r>
+  <r>
+    <s v="Programme"/>
+    <x v="10"/>
+    <x v="2"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDMonitoring.html"/>
+  </r>
+  <r>
+    <s v="GroundWaterBody_gwReasonsForRiskQuantitative"/>
+    <x v="11"/>
+    <x v="2"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDGroundWaterBody.html"/>
+  </r>
+  <r>
+    <s v="GWB"/>
+    <x v="11"/>
+    <x v="2"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDGroundWaterBody.html"/>
+  </r>
+  <r>
+    <s v="GWMET"/>
+    <x v="12"/>
+    <x v="2"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDGroundwaterMethodologies.html"/>
+  </r>
+  <r>
+    <s v="GWPressures_gwPressuresNotAssessed"/>
+    <x v="12"/>
+    <x v="2"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDGroundwaterMethodologies.html"/>
+  </r>
+  <r>
+    <s v="SWB"/>
+    <x v="0"/>
+    <x v="2"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDSurfaceWaterBody.html"/>
+  </r>
+  <r>
+    <s v="SWMET"/>
+    <x v="1"/>
+    <x v="2"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDSurfaceWaterMethodologies.html"/>
+  </r>
+  <r>
+    <s v="SWPressures_swPressuresNotAssessed"/>
+    <x v="1"/>
+    <x v="2"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDSurfaceWaterMethodologies.html"/>
+  </r>
+  <r>
+    <s v="CompetentAuthority"/>
+    <x v="3"/>
+    <x v="3"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDRiverBasinDistrictsAndCompetentAuthorities.html"/>
+  </r>
+  <r>
+    <s v="RBD"/>
+    <x v="3"/>
+    <x v="3"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDRiverBasinDistrictsAndCompetentAuthorities.html"/>
+  </r>
+  <r>
+    <s v="RBDSUCA"/>
+    <x v="3"/>
+    <x v="3"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDRiverBasinDistrictsAndCompetentAuthorities.html"/>
+  </r>
+  <r>
+    <s v="CoOrd"/>
+    <x v="4"/>
+    <x v="3"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDMeasures.html"/>
+  </r>
+  <r>
+    <s v="RBMP"/>
+    <x v="4"/>
+    <x v="3"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDMeasures.html"/>
+  </r>
+  <r>
+    <s v="RBMP_documentProvision"/>
+    <x v="4"/>
+    <x v="3"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDMeasures.html"/>
+  </r>
+  <r>
+    <s v="RBMP_impactPublicParticipation"/>
+    <x v="4"/>
+    <x v="3"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDMeasures.html"/>
+  </r>
+  <r>
+    <s v="RBMP_ongoingStakeholderInvolvement"/>
+    <x v="4"/>
+    <x v="3"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDMeasures.html"/>
+  </r>
+  <r>
+    <s v="RBMP_publicConsultationInformation"/>
+    <x v="4"/>
+    <x v="3"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDMeasures.html"/>
+  </r>
+  <r>
+    <s v="RBMP_rbmpConsultation"/>
+    <x v="4"/>
+    <x v="3"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDMeasures.html"/>
+  </r>
+  <r>
+    <s v="RBMP_stakeholderGroups"/>
+    <x v="4"/>
+    <x v="3"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDMeasures.html"/>
+  </r>
+  <r>
+    <s v="RBMP_subPlansCoverage"/>
+    <x v="4"/>
+    <x v="3"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDMeasures.html"/>
+  </r>
+  <r>
+    <s v="TargetedQ"/>
+    <x v="4"/>
+    <x v="3"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDMeasures.html"/>
+  </r>
+  <r>
+    <s v="TargetedQ_basicMeasuresArt113hIssues"/>
+    <x v="4"/>
+    <x v="3"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDMeasures.html"/>
+  </r>
+  <r>
+    <s v="TargetedQ_climateChangeAspectsConsidered"/>
+    <x v="4"/>
+    <x v="3"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDMeasures.html"/>
+  </r>
+  <r>
+    <s v="TargetedQ_msfdMeasuresNeeded"/>
+    <x v="4"/>
+    <x v="3"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDMeasures.html"/>
+  </r>
+  <r>
+    <s v="Costs"/>
+    <x v="5"/>
+    <x v="3"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDMeasures.html"/>
+  </r>
+  <r>
+    <s v="Measure"/>
+    <x v="5"/>
+    <x v="3"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDMeasures.html"/>
+  </r>
+  <r>
+    <s v="Progress"/>
+    <x v="5"/>
+    <x v="3"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDMeasures.html"/>
+  </r>
+  <r>
+    <s v="EconomicAnalysis"/>
+    <x v="8"/>
+    <x v="3"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDEconomicAnalysis.html"/>
+  </r>
+  <r>
+    <s v="Service"/>
+    <x v="8"/>
+    <x v="3"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDEconomicAnalysis.html"/>
+  </r>
+  <r>
+    <s v="GWAssociatedProtectedArea"/>
+    <x v="13"/>
+    <x v="3"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDProtectedAreas.html"/>
+  </r>
+  <r>
+    <s v="SWAssociatedProtectedArea"/>
+    <x v="13"/>
+    <x v="3"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDProtectedAreas.html"/>
+  </r>
+  <r>
+    <s v="GroundWaterBody_gwQuantitativeExemptionType"/>
+    <x v="9"/>
+    <x v="3"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDExemptions.html"/>
+  </r>
+  <r>
+    <s v="GWAssociatedProtectedArea_protectedAreaExemption"/>
+    <x v="9"/>
+    <x v="3"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDEconomicAnalysis.html"/>
+  </r>
+  <r>
+    <s v="GWChemicalExemptionType"/>
+    <x v="9"/>
+    <x v="3"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDEconomicAnalysis.html"/>
+  </r>
+  <r>
+    <s v="QualityElement_qeEcologicalExemptionType"/>
+    <x v="9"/>
+    <x v="3"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDEconomicAnalysis.html"/>
+  </r>
+  <r>
+    <s v="SWAssociatedProtectedArea_protectedAreaExemption"/>
+    <x v="9"/>
+    <x v="3"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDEconomicAnalysis.html"/>
+  </r>
+  <r>
+    <s v="SWChemicalExemptionType"/>
+    <x v="9"/>
+    <x v="3"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDEconomicAnalysis.html"/>
+  </r>
+  <r>
+    <s v="SWEcologicalExemptionType"/>
+    <x v="9"/>
+    <x v="3"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDEconomicAnalysis.html"/>
+  </r>
+  <r>
+    <s v="ChemicalEcologicalQuantitativeMonitoring"/>
+    <x v="10"/>
+    <x v="3"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDMonitoring.html"/>
+  </r>
+  <r>
+    <s v="MonitoringSite"/>
+    <x v="10"/>
+    <x v="3"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDMonitoring.html"/>
+  </r>
+  <r>
+    <s v="GroundWaterBody"/>
+    <x v="11"/>
+    <x v="3"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDGroundWaterBody.html"/>
+  </r>
+  <r>
+    <s v="GroundWaterBody_gwChemicalReasonsForFailure"/>
+    <x v="11"/>
+    <x v="3"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDGroundWaterBody.html"/>
+  </r>
+  <r>
+    <s v="GroundWaterBody_gwQuantitativeReasonsForFailure"/>
+    <x v="11"/>
+    <x v="3"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDGroundWaterBody.html"/>
+  </r>
+  <r>
+    <s v="GroundWaterBody_gwSignificantImpactType"/>
+    <x v="11"/>
+    <x v="3"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDGroundWaterBody.html"/>
+  </r>
+  <r>
+    <s v="GroundWaterBody_gwSignificantPressureType"/>
+    <x v="11"/>
+    <x v="3"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDGroundWaterBody.html"/>
+  </r>
+  <r>
+    <s v="GroundWaterBody_linkSurfaceWaterBodyCode"/>
+    <x v="11"/>
+    <x v="3"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDGroundWaterBody.html"/>
+  </r>
+  <r>
+    <s v="GWPollutant"/>
+    <x v="11"/>
+    <x v="3"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDGroundWaterBody.html"/>
+  </r>
+  <r>
+    <s v="GWMethodologies"/>
+    <x v="12"/>
+    <x v="3"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDGroundwaterMethodologies.html"/>
+  </r>
+  <r>
+    <s v="GWPressures"/>
+    <x v="12"/>
+    <x v="3"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDGroundwaterMethodologies.html"/>
+  </r>
+  <r>
+    <s v="ThresholdValue"/>
+    <x v="12"/>
+    <x v="3"/>
+    <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDGroundwaterMethodologies.html"/>
+  </r>
+  <r>
     <s v="SWChemicalStatusClassificationRBD"/>
-    <x v="12"/>
-    <x v="1"/>
+    <x v="1"/>
+    <x v="3"/>
     <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDSurfaceWaterMethodologies.html"/>
   </r>
   <r>
     <s v="SWManagementObjectives"/>
-    <x v="12"/>
-    <x v="1"/>
+    <x v="1"/>
+    <x v="3"/>
     <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDSurfaceWaterMethodologies.html"/>
   </r>
   <r>
     <s v="SWMethodologies"/>
-    <x v="12"/>
-    <x v="1"/>
+    <x v="1"/>
+    <x v="3"/>
     <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDSurfaceWaterMethodologies.html"/>
   </r>
   <r>
     <s v="SWPressures"/>
-    <x v="12"/>
-    <x v="1"/>
+    <x v="1"/>
+    <x v="3"/>
     <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDSurfaceWaterMethodologies.html"/>
   </r>
   <r>
     <s v="SWTargetedQ"/>
-    <x v="12"/>
-    <x v="1"/>
+    <x v="1"/>
+    <x v="3"/>
     <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDSurfaceWaterMethodologies.html"/>
   </r>
   <r>
     <s v="SWTargetedQ_bqeForMEPGEP"/>
-    <x v="12"/>
-    <x v="1"/>
+    <x v="1"/>
+    <x v="3"/>
     <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDSurfaceWaterMethodologies.html"/>
   </r>
   <r>
     <s v="SWTargetedQ_mitigationMeasures"/>
-    <x v="12"/>
-    <x v="1"/>
+    <x v="1"/>
+    <x v="3"/>
     <s v="https://eeadata.github.io/WISE.WFD.Documentation/DataModelReview/WFDSurfaceWaterMethodologies.html"/>
-  </r>
-  <r>
-    <s v="CoOrd_iRBMPReference"/>
-    <x v="13"/>
-    <x v="3"/>
-    <m/>
-  </r>
-  <r>
-    <s v="Costs_costExplanation20152021Reference"/>
-    <x v="13"/>
-    <x v="3"/>
-    <m/>
-  </r>
-  <r>
-    <s v="Costs_costExplanation20212027Reference"/>
-    <x v="13"/>
-    <x v="3"/>
-    <m/>
-  </r>
-  <r>
-    <s v="dcMetadata"/>
-    <x v="13"/>
-    <x v="3"/>
-    <m/>
-  </r>
-  <r>
-    <s v="EconomicAnalysis_article94Reference"/>
-    <x v="13"/>
-    <x v="3"/>
-    <m/>
-  </r>
-  <r>
-    <s v="EconomicAnalysis_costEffectivenessReference"/>
-    <x v="13"/>
-    <x v="3"/>
-    <m/>
-  </r>
-  <r>
-    <s v="EconomicAnalysis_costRecoveryReference"/>
-    <x v="13"/>
-    <x v="3"/>
-    <m/>
-  </r>
-  <r>
-    <s v="EconomicAnalysis_economicAnalysisReference"/>
-    <x v="13"/>
-    <x v="3"/>
-    <m/>
-  </r>
-  <r>
-    <s v="GWExemptions_driversGWExemptionsReference"/>
-    <x v="13"/>
-    <x v="3"/>
-    <m/>
-  </r>
-  <r>
-    <s v="GWExemptions_gwExemptionsReference"/>
-    <x v="13"/>
-    <x v="3"/>
-    <m/>
-  </r>
-  <r>
-    <s v="GWMethodologies_gwCharacterisationReference"/>
-    <x v="13"/>
-    <x v="3"/>
-    <m/>
-  </r>
-  <r>
-    <s v="GWMethodologies_gwMethodologiesChemicalClassificationReference"/>
-    <x v="13"/>
-    <x v="3"/>
-    <m/>
-  </r>
-  <r>
-    <s v="GWMethodologies_gwMethodologiesTransboundaryReference"/>
-    <x v="13"/>
-    <x v="3"/>
-    <m/>
-  </r>
-  <r>
-    <s v="GWMethodologies_gwMethQuantitativeClassificationReference"/>
-    <x v="13"/>
-    <x v="3"/>
-    <m/>
-  </r>
-  <r>
-    <s v="GWPressures_gwPressuresReference"/>
-    <x v="13"/>
-    <x v="3"/>
-    <m/>
-  </r>
-  <r>
-    <s v="InputInventory_inputInventoryReference"/>
-    <x v="13"/>
-    <x v="3"/>
-    <m/>
-  </r>
-  <r>
-    <s v="InputPollutant_inputMethodReference"/>
-    <x v="13"/>
-    <x v="3"/>
-    <m/>
-  </r>
-  <r>
-    <s v="Measure_measureReference"/>
-    <x v="13"/>
-    <x v="3"/>
-    <m/>
-  </r>
-  <r>
-    <s v="Metadata"/>
-    <x v="13"/>
-    <x v="3"/>
-    <m/>
-  </r>
-  <r>
-    <s v="Programme_programmeReference"/>
-    <x v="13"/>
-    <x v="3"/>
-    <m/>
-  </r>
-  <r>
-    <s v="Progress_measuresFromPreviousProgrammeReference"/>
-    <x v="13"/>
-    <x v="3"/>
-    <m/>
-  </r>
-  <r>
-    <s v="RBMP_consultationResponsesReference"/>
-    <x v="13"/>
-    <x v="3"/>
-    <m/>
-  </r>
-  <r>
-    <s v="RBMP_fdCoordinationReference"/>
-    <x v="13"/>
-    <x v="3"/>
-    <m/>
-  </r>
-  <r>
-    <s v="RBMP_msfdCoordinationReference"/>
-    <x v="13"/>
-    <x v="3"/>
-    <m/>
-  </r>
-  <r>
-    <s v="RBMP_publicParticipationReference"/>
-    <x v="13"/>
-    <x v="3"/>
-    <m/>
-  </r>
-  <r>
-    <s v="RBMP_seaReference"/>
-    <x v="13"/>
-    <x v="3"/>
-    <m/>
-  </r>
-  <r>
-    <s v="RBMP_subPlansReference"/>
-    <x v="13"/>
-    <x v="3"/>
-    <m/>
-  </r>
-  <r>
-    <s v="ReferenceType"/>
-    <x v="13"/>
-    <x v="3"/>
-    <m/>
-  </r>
-  <r>
-    <s v="Service_serviceCostInstrumentReference"/>
-    <x v="13"/>
-    <x v="3"/>
-    <m/>
-  </r>
-  <r>
-    <s v="SWChemicalStatusClassificationRBD_bioavailabilityReference"/>
-    <x v="13"/>
-    <x v="3"/>
-    <m/>
-  </r>
-  <r>
-    <s v="SWChemicalStatusClassificationRBD_chemicalStatusReference"/>
-    <x v="13"/>
-    <x v="3"/>
-    <m/>
-  </r>
-  <r>
-    <s v="SWChemicalStatusClassificationRBD_longTermTrendAnalysisReference"/>
-    <x v="13"/>
-    <x v="3"/>
-    <m/>
-  </r>
-  <r>
-    <s v="SWChemStClassRBD_alternativeMixingZoneMethodologyReference"/>
-    <x v="13"/>
-    <x v="3"/>
-    <m/>
-  </r>
-  <r>
-    <s v="SWChemStClassRBD_approachSWBNotMonitoredChemicalReference"/>
-    <x v="13"/>
-    <x v="3"/>
-    <m/>
-  </r>
-  <r>
-    <s v="SWChemStClassRBD_backgroundConcentrationsReference"/>
-    <x v="13"/>
-    <x v="3"/>
-    <m/>
-  </r>
-  <r>
-    <s v="SWChemStClassRBD_mixingZoneMeasuresReductionReference"/>
-    <x v="13"/>
-    <x v="3"/>
-    <m/>
-  </r>
-  <r>
-    <s v="SWExemptions_driversSWExemptionsReference"/>
-    <x v="13"/>
-    <x v="3"/>
-    <m/>
-  </r>
-  <r>
-    <s v="SWExemptions_swExemptionsReference"/>
-    <x v="13"/>
-    <x v="3"/>
-    <m/>
-  </r>
-  <r>
-    <s v="SWManagementObjectives_managementObjectivesReference"/>
-    <x v="13"/>
-    <x v="3"/>
-    <m/>
-  </r>
-  <r>
-    <s v="SWManagementObjectives_waterResourcePlansReference"/>
-    <x v="13"/>
-    <x v="3"/>
-    <m/>
-  </r>
-  <r>
-    <s v="SWMethodologies_hmwbMethodologyReference"/>
-    <x v="13"/>
-    <x v="3"/>
-    <m/>
-  </r>
-  <r>
-    <s v="SWMethodologies_iRBDTypologyCoOrdinationReference"/>
-    <x v="13"/>
-    <x v="3"/>
-    <m/>
-  </r>
-  <r>
-    <s v="SWMethodologies_smallWBsMethodologyReference"/>
-    <x v="13"/>
-    <x v="3"/>
-    <m/>
-  </r>
-  <r>
-    <s v="SWMethodologies_typologyMethodologyReference"/>
-    <x v="13"/>
-    <x v="3"/>
-    <m/>
-  </r>
-  <r>
-    <s v="SWPressures_swPressuresReference"/>
-    <x v="13"/>
-    <x v="3"/>
-    <m/>
-  </r>
-  <r>
-    <s v="SWTargetedQ_driversFailureEcologicalStatusPotentialReference"/>
-    <x v="13"/>
-    <x v="3"/>
-    <m/>
-  </r>
-  <r>
-    <s v="SWTargetedQ_ecologicalStatusMethodReference"/>
-    <x v="13"/>
-    <x v="3"/>
-    <m/>
-  </r>
-  <r>
-    <s v="SWTargetedQ_gepMethodReference"/>
-    <x v="13"/>
-    <x v="3"/>
-    <m/>
-  </r>
-  <r>
-    <s v="TargetedQ_basicMeasuresArt113b-lReference"/>
-    <x v="13"/>
-    <x v="3"/>
-    <m/>
-  </r>
-  <r>
-    <s v="TargetedQ_otherAspectsReference"/>
-    <x v="13"/>
-    <x v="3"/>
-    <m/>
-  </r>
-  <r>
-    <s v="WaterQuantity_wqAlternativeIndicatorReference"/>
-    <x v="13"/>
-    <x v="3"/>
-    <m/>
-  </r>
-  <r>
-    <s v="WaterQuantity_wqCalculationMethodReference"/>
-    <x v="13"/>
-    <x v="3"/>
-    <m/>
-  </r>
-  <r>
-    <s v="WFDCommon"/>
-    <x v="13"/>
-    <x v="3"/>
-    <m/>
   </r>
   <r>
     <m/>
@@ -2452,36 +2119,36 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6D907F6D-6BCB-457A-ACE7-59E109D8D8D8}" name="PivotTable2" cacheId="29" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6D907F6D-6BCB-457A-ACE7-59E109D8D8D8}" name="PivotTable2" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:F19" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="4">
     <pivotField dataField="1" showAll="0"/>
     <pivotField axis="axisRow" showAll="0" sortType="ascending">
       <items count="16">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
         <item x="3"/>
         <item x="4"/>
         <item x="5"/>
         <item x="6"/>
         <item x="7"/>
         <item x="8"/>
+        <item x="13"/>
         <item x="9"/>
         <item x="10"/>
         <item x="11"/>
         <item x="12"/>
-        <item x="13"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
         <item h="1" x="14"/>
         <item t="default"/>
       </items>
     </pivotField>
     <pivotField axis="axisCol" showAll="0">
       <items count="6">
+        <item x="3"/>
+        <item x="2"/>
+        <item x="0"/>
         <item x="1"/>
-        <item x="0"/>
-        <item x="2"/>
-        <item x="3"/>
         <item h="1" x="4"/>
         <item t="default"/>
       </items>
@@ -2562,25 +2229,25 @@
     <dataField name="Count of tablenameAccessDatabase" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="9">
-    <format dxfId="64">
+    <format dxfId="17">
       <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="63">
+    <format dxfId="16">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="62">
+    <format dxfId="15">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="61">
+    <format dxfId="14">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="60">
+    <format dxfId="13">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="59">
+    <format dxfId="12">
       <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="58">
+    <format dxfId="11">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="3">
@@ -2591,10 +2258,10 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="57">
+    <format dxfId="10">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="0">
+    <format dxfId="9">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="1">
@@ -2945,42 +2612,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="16" t="s">
         <v>217</v>
       </c>
-      <c r="B1" s="23" t="s">
+      <c r="B1" s="16" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="14" t="s">
         <v>191</v>
       </c>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="14" t="s">
         <v>189</v>
       </c>
-      <c r="B4" s="21" t="s">
+      <c r="B4" s="14" t="s">
         <v>172</v>
       </c>
-      <c r="C4" s="21" t="s">
-        <v>170</v>
-      </c>
-      <c r="D4" s="21" t="s">
+      <c r="C4" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="D4" s="14" t="s">
         <v>184</v>
       </c>
-      <c r="E4" s="21" t="s">
-        <v>174</v>
-      </c>
-      <c r="F4" s="21" t="s">
+      <c r="E4" s="14" t="s">
+        <v>174</v>
+      </c>
+      <c r="F4" s="14" t="s">
         <v>190</v>
       </c>
     </row>
@@ -2988,15 +2655,15 @@
       <c r="A5" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="B5" s="18">
+      <c r="B5" s="21">
         <v>3</v>
       </c>
-      <c r="C5" s="18">
+      <c r="C5" s="21">
         <v>5</v>
       </c>
-      <c r="D5" s="18"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="18">
+      <c r="D5" s="21"/>
+      <c r="E5" s="21"/>
+      <c r="F5" s="21">
         <v>8</v>
       </c>
     </row>
@@ -3004,15 +2671,15 @@
       <c r="A6" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="B6" s="18">
+      <c r="B6" s="21">
         <v>13</v>
       </c>
-      <c r="C6" s="18">
+      <c r="C6" s="21">
         <v>1</v>
       </c>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18">
+      <c r="D6" s="21"/>
+      <c r="E6" s="21"/>
+      <c r="F6" s="21">
         <v>14</v>
       </c>
     </row>
@@ -3020,15 +2687,15 @@
       <c r="A7" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="B7" s="18">
+      <c r="B7" s="21">
         <v>3</v>
       </c>
-      <c r="C7" s="18">
+      <c r="C7" s="21">
         <v>6</v>
       </c>
-      <c r="D7" s="18"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="18">
+      <c r="D7" s="21"/>
+      <c r="E7" s="21"/>
+      <c r="F7" s="21">
         <v>9</v>
       </c>
     </row>
@@ -3036,13 +2703,13 @@
       <c r="A8" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="B8" s="18"/>
-      <c r="C8" s="18">
+      <c r="B8" s="21"/>
+      <c r="C8" s="21">
         <v>5</v>
       </c>
-      <c r="D8" s="18"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="18">
+      <c r="D8" s="21"/>
+      <c r="E8" s="21"/>
+      <c r="F8" s="21">
         <v>5</v>
       </c>
     </row>
@@ -3050,13 +2717,13 @@
       <c r="A9" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="B9" s="18"/>
-      <c r="C9" s="18">
+      <c r="B9" s="21"/>
+      <c r="C9" s="21">
         <v>2</v>
       </c>
-      <c r="D9" s="18"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="18">
+      <c r="D9" s="21"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="21">
         <v>2</v>
       </c>
     </row>
@@ -3064,15 +2731,15 @@
       <c r="A10" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="B10" s="18">
+      <c r="B10" s="21">
         <v>2</v>
       </c>
-      <c r="C10" s="18">
+      <c r="C10" s="21">
         <v>1</v>
       </c>
-      <c r="D10" s="18"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="18">
+      <c r="D10" s="21"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="21">
         <v>3</v>
       </c>
     </row>
@@ -3080,13 +2747,13 @@
       <c r="A11" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="B11" s="18">
+      <c r="B11" s="21">
         <v>2</v>
       </c>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18">
+      <c r="C11" s="21"/>
+      <c r="D11" s="21"/>
+      <c r="E11" s="21"/>
+      <c r="F11" s="21">
         <v>2</v>
       </c>
     </row>
@@ -3094,15 +2761,15 @@
       <c r="A12" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="B12" s="18">
+      <c r="B12" s="21">
         <v>7</v>
       </c>
-      <c r="C12" s="18">
+      <c r="C12" s="21">
         <v>25</v>
       </c>
-      <c r="D12" s="18"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="18">
+      <c r="D12" s="21"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="21">
         <v>32</v>
       </c>
     </row>
@@ -3110,15 +2777,15 @@
       <c r="A13" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="B13" s="18">
+      <c r="B13" s="21">
         <v>2</v>
       </c>
-      <c r="C13" s="18">
+      <c r="C13" s="21">
         <v>3</v>
       </c>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18">
+      <c r="D13" s="21"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="21">
         <v>5</v>
       </c>
     </row>
@@ -3126,15 +2793,15 @@
       <c r="A14" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="B14" s="18">
+      <c r="B14" s="21">
         <v>7</v>
       </c>
-      <c r="C14" s="18">
+      <c r="C14" s="21">
         <v>2</v>
       </c>
-      <c r="D14" s="18"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="18">
+      <c r="D14" s="21"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="21">
         <v>9</v>
       </c>
     </row>
@@ -3142,17 +2809,15 @@
       <c r="A15" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B15" s="18">
+      <c r="B15" s="21">
+        <v>3</v>
+      </c>
+      <c r="C15" s="21">
         <v>2</v>
       </c>
-      <c r="C15" s="18">
-        <v>2</v>
-      </c>
-      <c r="D15" s="18">
-        <v>1</v>
-      </c>
-      <c r="E15" s="18"/>
-      <c r="F15" s="18">
+      <c r="D15" s="21"/>
+      <c r="E15" s="21"/>
+      <c r="F15" s="21">
         <v>5</v>
       </c>
     </row>
@@ -3160,15 +2825,15 @@
       <c r="A16" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="B16" s="18"/>
-      <c r="C16" s="18">
+      <c r="B16" s="21"/>
+      <c r="C16" s="21">
         <v>1</v>
       </c>
-      <c r="D16" s="18">
+      <c r="D16" s="21">
         <v>11</v>
       </c>
-      <c r="E16" s="18"/>
-      <c r="F16" s="18">
+      <c r="E16" s="21"/>
+      <c r="F16" s="21">
         <v>12</v>
       </c>
     </row>
@@ -3176,17 +2841,17 @@
       <c r="A17" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="B17" s="18">
+      <c r="B17" s="21">
         <v>7</v>
       </c>
-      <c r="C17" s="18">
+      <c r="C17" s="21">
         <v>2</v>
       </c>
-      <c r="D17" s="18">
+      <c r="D17" s="21">
         <v>10</v>
       </c>
-      <c r="E17" s="18"/>
-      <c r="F17" s="18">
+      <c r="E17" s="21"/>
+      <c r="F17" s="21">
         <v>19</v>
       </c>
     </row>
@@ -3194,33 +2859,33 @@
       <c r="A18" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="B18" s="18"/>
-      <c r="C18" s="18"/>
-      <c r="D18" s="18"/>
-      <c r="E18" s="18">
+      <c r="B18" s="21"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="21">
         <v>53</v>
       </c>
-      <c r="F18" s="18">
+      <c r="F18" s="21">
         <v>53</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A19" s="19" t="s">
+      <c r="A19" s="13" t="s">
         <v>190</v>
       </c>
-      <c r="B19" s="20">
-        <v>48</v>
-      </c>
-      <c r="C19" s="20">
+      <c r="B19" s="22">
+        <v>49</v>
+      </c>
+      <c r="C19" s="22">
         <v>55</v>
       </c>
-      <c r="D19" s="20">
-        <v>22</v>
-      </c>
-      <c r="E19" s="20">
+      <c r="D19" s="22">
+        <v>21</v>
+      </c>
+      <c r="E19" s="22">
         <v>53</v>
       </c>
-      <c r="F19" s="20">
+      <c r="F19" s="22">
         <v>178</v>
       </c>
     </row>
@@ -3234,368 +2899,361 @@
   <dimension ref="A1:E179"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="56.796875" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.1328125" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="80.46484375" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.06640625" style="7"/>
-    <col min="6" max="16384" width="9.06640625" style="6"/>
+    <col min="1" max="1" width="56.796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.1328125" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.59765625" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="80.46484375" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.06640625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="16" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:5" s="12" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="9" t="s">
         <v>204</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="10" t="s">
         <v>183</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="11" t="s">
         <v>171</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="E1" s="14"/>
+      <c r="E1" s="10"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A2" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>198</v>
-      </c>
-      <c r="C2" s="10" t="s">
+      <c r="A2" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="D2" s="17" t="s">
-        <v>185</v>
-      </c>
-      <c r="E2" s="6"/>
+      <c r="D2" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="E2"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A3" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>198</v>
-      </c>
-      <c r="C3" s="10" t="s">
+      <c r="A3" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="D3" s="17" t="s">
-        <v>185</v>
-      </c>
-      <c r="E3" s="6"/>
+      <c r="D3" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="E3"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A4" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="7" t="s">
+      <c r="A4" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="E4" s="6"/>
+      <c r="E4"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B5" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="E5" s="6"/>
+      <c r="E5"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="B6" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="E6" s="6"/>
+      <c r="E6"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="B7" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="E7" s="6"/>
+      <c r="E7"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="B8" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="E8" s="6"/>
+      <c r="E8"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="B9" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="20" t="s">
         <v>184</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="E9" s="6"/>
+      <c r="E9"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A10" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="B10" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="E10" s="6"/>
+      <c r="E10"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A11" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="B11" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>197</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="E11" s="6"/>
+      <c r="E11"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A12" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="B12" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="E12" s="6"/>
+      <c r="E12"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A13" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="C13" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="C13" s="20" t="s">
         <v>184</v>
       </c>
-      <c r="D13" s="7" t="s">
-        <v>187</v>
-      </c>
-      <c r="E13" s="6"/>
+      <c r="D13" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="E13"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A14" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="C14" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="C14" s="20" t="s">
         <v>184</v>
       </c>
-      <c r="D14" s="7" t="s">
-        <v>187</v>
+      <c r="D14" s="3" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A15" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B15" s="7" t="s">
+      <c r="A15" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>199</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="D15" s="3" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A16" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B16" s="7" t="s">
+      <c r="A16" t="s">
+        <v>142</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>199</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="D16" s="3" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A17" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="B17" s="7" t="s">
+      <c r="A17" t="s">
+        <v>143</v>
+      </c>
+      <c r="B17" s="3" t="s">
         <v>199</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="D17" s="3" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A18" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="B18" s="7" t="s">
+      <c r="A18" t="s">
+        <v>147</v>
+      </c>
+      <c r="B18" s="3" t="s">
         <v>199</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="D18" s="3" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A19" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="B19" s="7" t="s">
+      <c r="A19" t="s">
+        <v>148</v>
+      </c>
+      <c r="B19" s="3" t="s">
         <v>199</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="D19" s="3" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A20" s="11" t="s">
-        <v>147</v>
-      </c>
-      <c r="B20" s="7" t="s">
+      <c r="A20" t="s">
+        <v>149</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>199</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="D20" s="7" t="s">
+      <c r="D20" s="3" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A21" s="11" t="s">
-        <v>148</v>
-      </c>
-      <c r="B21" s="7" t="s">
+      <c r="A21" s="18" t="s">
+        <v>156</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>199</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="D21" s="7" t="s">
+      <c r="D21" s="3" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A22" s="11" t="s">
-        <v>149</v>
-      </c>
-      <c r="B22" s="7" t="s">
+      <c r="A22" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="B22" s="3" t="s">
         <v>199</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="D22" s="7" t="s">
+      <c r="D22" s="3" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A23" s="8" t="s">
-        <v>156</v>
-      </c>
-      <c r="B23" s="7" t="s">
-        <v>199</v>
+      <c r="A23" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>173</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A24" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>199</v>
+      <c r="A24" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>173</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A25" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B25" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B25" s="3" t="s">
         <v>173</v>
       </c>
       <c r="C25" s="4" t="s">
@@ -3604,9 +3262,9 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A26" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B26" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B26" s="3" t="s">
         <v>173</v>
       </c>
       <c r="C26" s="4" t="s">
@@ -3615,9 +3273,9 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A27" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B27" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B27" s="3" t="s">
         <v>173</v>
       </c>
       <c r="C27" s="4" t="s">
@@ -3626,9 +3284,9 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A28" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B28" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B28" s="3" t="s">
         <v>173</v>
       </c>
       <c r="C28" s="4" t="s">
@@ -3637,9 +3295,9 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A29" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B29" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B29" s="3" t="s">
         <v>173</v>
       </c>
       <c r="C29" s="4" t="s">
@@ -3648,9 +3306,9 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A30" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B30" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B30" s="3" t="s">
         <v>173</v>
       </c>
       <c r="C30" s="4" t="s">
@@ -3659,9 +3317,9 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A31" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B31" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B31" s="3" t="s">
         <v>173</v>
       </c>
       <c r="C31" s="4" t="s">
@@ -3670,9 +3328,9 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A32" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B32" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" s="3" t="s">
         <v>173</v>
       </c>
       <c r="C32" s="4" t="s">
@@ -3681,9 +3339,9 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A33" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B33" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B33" s="3" t="s">
         <v>173</v>
       </c>
       <c r="C33" s="4" t="s">
@@ -3692,9 +3350,9 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A34" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B34" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B34" s="3" t="s">
         <v>173</v>
       </c>
       <c r="C34" s="4" t="s">
@@ -3703,9 +3361,9 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A35" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B35" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B35" s="3" t="s">
         <v>173</v>
       </c>
       <c r="C35" s="4" t="s">
@@ -3714,9 +3372,9 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A36" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B36" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B36" s="3" t="s">
         <v>173</v>
       </c>
       <c r="C36" s="4" t="s">
@@ -3725,9 +3383,9 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A37" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B37" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B37" s="3" t="s">
         <v>173</v>
       </c>
       <c r="C37" s="4" t="s">
@@ -3736,9 +3394,9 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A38" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B38" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B38" s="3" t="s">
         <v>173</v>
       </c>
       <c r="C38" s="4" t="s">
@@ -3747,9 +3405,9 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A39" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B39" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B39" s="3" t="s">
         <v>173</v>
       </c>
       <c r="C39" s="4" t="s">
@@ -3758,9 +3416,9 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A40" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B40" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="B40" s="3" t="s">
         <v>173</v>
       </c>
       <c r="C40" s="4" t="s">
@@ -3769,9 +3427,9 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A41" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B41" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="B41" s="3" t="s">
         <v>173</v>
       </c>
       <c r="C41" s="4" t="s">
@@ -3780,9 +3438,9 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A42" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B42" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="B42" s="3" t="s">
         <v>173</v>
       </c>
       <c r="C42" s="4" t="s">
@@ -3791,9 +3449,9 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A43" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B43" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B43" s="3" t="s">
         <v>173</v>
       </c>
       <c r="C43" s="4" t="s">
@@ -3802,9 +3460,9 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A44" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B44" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B44" s="3" t="s">
         <v>173</v>
       </c>
       <c r="C44" s="4" t="s">
@@ -3813,9 +3471,9 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A45" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="B45" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="B45" s="3" t="s">
         <v>173</v>
       </c>
       <c r="C45" s="4" t="s">
@@ -3824,9 +3482,9 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A46" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="B46" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="B46" s="3" t="s">
         <v>173</v>
       </c>
       <c r="C46" s="4" t="s">
@@ -3835,9 +3493,9 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A47" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="B47" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="B47" s="3" t="s">
         <v>173</v>
       </c>
       <c r="C47" s="4" t="s">
@@ -3846,9 +3504,9 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A48" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="B48" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="B48" s="3" t="s">
         <v>173</v>
       </c>
       <c r="C48" s="4" t="s">
@@ -3857,9 +3515,9 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A49" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="B49" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="B49" s="3" t="s">
         <v>173</v>
       </c>
       <c r="C49" s="4" t="s">
@@ -3868,9 +3526,9 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A50" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="B50" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="B50" s="3" t="s">
         <v>173</v>
       </c>
       <c r="C50" s="4" t="s">
@@ -3879,9 +3537,9 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A51" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="B51" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="B51" s="3" t="s">
         <v>173</v>
       </c>
       <c r="C51" s="4" t="s">
@@ -3890,9 +3548,9 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A52" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B52" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="B52" s="3" t="s">
         <v>173</v>
       </c>
       <c r="C52" s="4" t="s">
@@ -3901,9 +3559,9 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A53" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="B53" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="B53" s="3" t="s">
         <v>173</v>
       </c>
       <c r="C53" s="4" t="s">
@@ -3912,9 +3570,9 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A54" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="B54" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="B54" s="3" t="s">
         <v>173</v>
       </c>
       <c r="C54" s="4" t="s">
@@ -3923,9 +3581,9 @@
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A55" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="B55" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="B55" s="3" t="s">
         <v>173</v>
       </c>
       <c r="C55" s="4" t="s">
@@ -3934,9 +3592,9 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A56" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="B56" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="B56" s="3" t="s">
         <v>173</v>
       </c>
       <c r="C56" s="4" t="s">
@@ -3945,9 +3603,9 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A57" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="B57" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="B57" s="3" t="s">
         <v>173</v>
       </c>
       <c r="C57" s="4" t="s">
@@ -3956,9 +3614,9 @@
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A58" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="B58" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="B58" s="3" t="s">
         <v>173</v>
       </c>
       <c r="C58" s="4" t="s">
@@ -3967,9 +3625,9 @@
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A59" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="B59" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="B59" s="3" t="s">
         <v>173</v>
       </c>
       <c r="C59" s="4" t="s">
@@ -3977,10 +3635,10 @@
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A60" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="B60" s="7" t="s">
+      <c r="A60" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="B60" s="3" t="s">
         <v>173</v>
       </c>
       <c r="C60" s="4" t="s">
@@ -3988,10 +3646,10 @@
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A61" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="B61" s="7" t="s">
+      <c r="A61" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="B61" s="3" t="s">
         <v>173</v>
       </c>
       <c r="C61" s="4" t="s">
@@ -3999,10 +3657,10 @@
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A62" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="B62" s="7" t="s">
+      <c r="A62" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="B62" s="3" t="s">
         <v>173</v>
       </c>
       <c r="C62" s="4" t="s">
@@ -4010,10 +3668,10 @@
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A63" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="B63" s="7" t="s">
+      <c r="A63" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="B63" s="3" t="s">
         <v>173</v>
       </c>
       <c r="C63" s="4" t="s">
@@ -4021,10 +3679,10 @@
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A64" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="B64" s="7" t="s">
+      <c r="A64" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="B64" s="3" t="s">
         <v>173</v>
       </c>
       <c r="C64" s="4" t="s">
@@ -4032,10 +3690,10 @@
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A65" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="B65" s="7" t="s">
+      <c r="A65" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="B65" s="3" t="s">
         <v>173</v>
       </c>
       <c r="C65" s="4" t="s">
@@ -4043,10 +3701,10 @@
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A66" s="8" t="s">
-        <v>139</v>
-      </c>
-      <c r="B66" s="7" t="s">
+      <c r="A66" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="B66" s="3" t="s">
         <v>173</v>
       </c>
       <c r="C66" s="4" t="s">
@@ -4054,10 +3712,10 @@
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A67" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="B67" s="7" t="s">
+      <c r="A67" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="B67" s="3" t="s">
         <v>173</v>
       </c>
       <c r="C67" s="4" t="s">
@@ -4065,10 +3723,10 @@
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A68" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="B68" s="7" t="s">
+      <c r="A68" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="B68" s="3" t="s">
         <v>173</v>
       </c>
       <c r="C68" s="4" t="s">
@@ -4076,10 +3734,10 @@
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A69" s="8" t="s">
-        <v>146</v>
-      </c>
-      <c r="B69" s="7" t="s">
+      <c r="A69" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="B69" s="3" t="s">
         <v>173</v>
       </c>
       <c r="C69" s="4" t="s">
@@ -4087,10 +3745,10 @@
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A70" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="B70" s="7" t="s">
+      <c r="A70" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="B70" s="3" t="s">
         <v>173</v>
       </c>
       <c r="C70" s="4" t="s">
@@ -4098,10 +3756,10 @@
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A71" s="8" t="s">
-        <v>153</v>
-      </c>
-      <c r="B71" s="7" t="s">
+      <c r="A71" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="B71" s="3" t="s">
         <v>173</v>
       </c>
       <c r="C71" s="4" t="s">
@@ -4109,10 +3767,10 @@
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A72" s="8" t="s">
-        <v>154</v>
-      </c>
-      <c r="B72" s="7" t="s">
+      <c r="A72" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="B72" s="3" t="s">
         <v>173</v>
       </c>
       <c r="C72" s="4" t="s">
@@ -4120,10 +3778,10 @@
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A73" s="8" t="s">
-        <v>159</v>
-      </c>
-      <c r="B73" s="7" t="s">
+      <c r="A73" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="B73" s="3" t="s">
         <v>173</v>
       </c>
       <c r="C73" s="4" t="s">
@@ -4131,10 +3789,10 @@
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A74" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="B74" s="7" t="s">
+      <c r="A74" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="B74" s="3" t="s">
         <v>173</v>
       </c>
       <c r="C74" s="4" t="s">
@@ -4142,10 +3800,10 @@
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A75" s="8" t="s">
-        <v>166</v>
-      </c>
-      <c r="B75" s="7" t="s">
+      <c r="A75" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="B75" s="3" t="s">
         <v>173</v>
       </c>
       <c r="C75" s="4" t="s">
@@ -4153,1366 +3811,1372 @@
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A76" s="8" t="s">
-        <v>167</v>
-      </c>
-      <c r="B76" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="C76" s="4" t="s">
-        <v>174</v>
+      <c r="A76" s="15" t="s">
+        <v>207</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C76" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A77" s="8" t="s">
-        <v>168</v>
-      </c>
-      <c r="B77" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="C77" s="4" t="s">
-        <v>174</v>
+      <c r="A77" s="15" t="s">
+        <v>208</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C77" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A78" s="22" t="s">
-        <v>207</v>
-      </c>
-      <c r="B78" s="7" t="s">
+      <c r="A78" s="15" t="s">
+        <v>210</v>
+      </c>
+      <c r="B78" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="C78" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="D78" s="7" t="s">
+      <c r="C78" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="D78" s="3" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A79" s="22" t="s">
-        <v>208</v>
-      </c>
-      <c r="B79" s="7" t="s">
+      <c r="A79" s="15" t="s">
+        <v>211</v>
+      </c>
+      <c r="B79" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="C79" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="D79" s="7" t="s">
+      <c r="C79" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="D79" s="3" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A80" s="22" t="s">
-        <v>210</v>
-      </c>
-      <c r="B80" s="7" t="s">
+      <c r="A80" s="15" t="s">
+        <v>212</v>
+      </c>
+      <c r="B80" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="C80" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="D80" s="7" t="s">
+      <c r="C80" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="D80" s="3" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A81" s="22" t="s">
-        <v>211</v>
-      </c>
-      <c r="B81" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="C81" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="D81" s="7" t="s">
-        <v>215</v>
+      <c r="A81" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A82" s="22" t="s">
-        <v>212</v>
-      </c>
-      <c r="B82" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="C82" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="D82" s="7" t="s">
-        <v>215</v>
+      <c r="A82" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="C82" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A83" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="B83" s="7" t="s">
-        <v>200</v>
+        <v>60</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="C83" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="D83" s="7" t="s">
+      <c r="D83" s="3" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A84" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B84" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="B84" s="3" t="s">
         <v>201</v>
       </c>
       <c r="C84" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="D84" s="7" t="s">
+      <c r="D84" s="3" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A85" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B85" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="B85" s="3" t="s">
         <v>201</v>
       </c>
       <c r="C85" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="D85" s="7" t="s">
+      <c r="D85" s="3" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A86" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B86" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="B86" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="C86" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="D86" s="7" t="s">
+      <c r="C86" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="D86" s="3" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A87" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B87" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="B87" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="C87" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="D87" s="7" t="s">
+      <c r="C87" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="D87" s="3" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A88" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B88" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="C88" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="D88" s="7" t="s">
-        <v>181</v>
+        <v>53</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A89" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="B89" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="C89" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="D89" s="7" t="s">
-        <v>181</v>
+        <v>54</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A90" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B90" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B90" s="3" t="s">
         <v>202</v>
       </c>
       <c r="C90" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="D90" s="7" t="s">
+      <c r="D90" s="3" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A91" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B91" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B91" s="3" t="s">
         <v>202</v>
       </c>
       <c r="C91" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="D91" s="7" t="s">
+      <c r="D91" s="3" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A92" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B92" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="B92" s="3" t="s">
         <v>202</v>
       </c>
       <c r="C92" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="D92" s="7" t="s">
+      <c r="D92" s="3" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A93" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B93" s="7" t="s">
-        <v>202</v>
+        <v>165</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>203</v>
       </c>
       <c r="C93" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="D93" s="7" t="s">
-        <v>175</v>
+      <c r="D93" s="3" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A94" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B94" s="7" t="s">
-        <v>202</v>
+        <v>169</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>203</v>
       </c>
       <c r="C94" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="D94" s="7" t="s">
-        <v>175</v>
+      <c r="D94" s="3" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A95" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="B95" s="7" t="s">
-        <v>203</v>
+        <v>95</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>193</v>
       </c>
       <c r="C95" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="D95" s="7" t="s">
-        <v>176</v>
+      <c r="D95" s="3" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A96" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="B96" s="7" t="s">
-        <v>203</v>
+      <c r="A96" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>194</v>
       </c>
       <c r="C96" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="D96" s="7" t="s">
-        <v>176</v>
+      <c r="D96" s="3" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A97" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="B97" s="7" t="s">
-        <v>193</v>
+        <v>28</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>194</v>
       </c>
       <c r="C97" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="D97" s="7" t="s">
-        <v>178</v>
+      <c r="D97" s="3" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A98" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B98" s="7" t="s">
+      <c r="A98" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B98" s="3" t="s">
         <v>194</v>
       </c>
       <c r="C98" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="D98" s="7" t="s">
+      <c r="D98" s="3" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A99" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B99" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B99" s="3" t="s">
         <v>194</v>
       </c>
       <c r="C99" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="D99" s="7" t="s">
+      <c r="D99" s="3" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A100" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B100" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B100" s="3" t="s">
         <v>194</v>
       </c>
       <c r="C100" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="D100" s="7" t="s">
+      <c r="D100" s="3" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A101" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B101" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B101" s="3" t="s">
         <v>194</v>
       </c>
       <c r="C101" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="D101" s="7" t="s">
+      <c r="D101" s="3" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A102" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B102" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B102" s="3" t="s">
         <v>194</v>
       </c>
       <c r="C102" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="D102" s="7" t="s">
+      <c r="D102" s="3" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A103" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B103" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B103" s="3" t="s">
         <v>194</v>
       </c>
       <c r="C103" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="D103" s="7" t="s">
+      <c r="D103" s="3" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A104" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B104" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B104" s="3" t="s">
         <v>194</v>
       </c>
       <c r="C104" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="D104" s="7" t="s">
+      <c r="D104" s="3" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A105" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B105" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B105" s="3" t="s">
         <v>194</v>
       </c>
       <c r="C105" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="D105" s="7" t="s">
+      <c r="D105" s="3" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A106" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B106" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B106" s="3" t="s">
         <v>194</v>
       </c>
       <c r="C106" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="D106" s="7" t="s">
+      <c r="D106" s="3" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A107" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B107" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B107" s="3" t="s">
         <v>194</v>
       </c>
       <c r="C107" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="D107" s="7" t="s">
+      <c r="D107" s="3" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A108" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B108" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B108" s="3" t="s">
         <v>194</v>
       </c>
       <c r="C108" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="D108" s="7" t="s">
+      <c r="D108" s="3" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A109" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B109" s="7" t="s">
+      <c r="A109" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="B109" s="3" t="s">
         <v>194</v>
       </c>
       <c r="C109" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="D109" s="7" t="s">
+      <c r="D109" s="3" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A110" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B110" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="B110" s="3" t="s">
         <v>194</v>
       </c>
       <c r="C110" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="D110" s="7" t="s">
+      <c r="D110" s="3" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A111" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="B111" s="7" t="s">
+      <c r="A111" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B111" s="3" t="s">
         <v>194</v>
       </c>
       <c r="C111" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="D111" s="7" t="s">
+      <c r="D111" s="3" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A112" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="B112" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="B112" s="3" t="s">
         <v>194</v>
       </c>
       <c r="C112" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="D112" s="7" t="s">
+      <c r="D112" s="3" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A113" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="B113" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="B113" s="3" t="s">
         <v>194</v>
       </c>
       <c r="C113" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="D113" s="7" t="s">
+      <c r="D113" s="3" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A114" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="B114" s="7" t="s">
+      <c r="A114" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="B114" s="3" t="s">
         <v>194</v>
       </c>
       <c r="C114" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="D114" s="7" t="s">
+      <c r="D114" s="3" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A115" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="B115" s="7" t="s">
+      <c r="A115" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="B115" s="3" t="s">
         <v>194</v>
       </c>
       <c r="C115" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="D115" s="7" t="s">
+      <c r="D115" s="3" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A116" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="B116" s="7" t="s">
+      <c r="A116" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="B116" s="3" t="s">
         <v>194</v>
       </c>
       <c r="C116" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="D116" s="7" t="s">
+      <c r="D116" s="3" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A117" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="B117" s="7" t="s">
+      <c r="A117" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="B117" s="3" t="s">
         <v>194</v>
       </c>
       <c r="C117" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="D117" s="7" t="s">
+      <c r="D117" s="3" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A118" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="B118" s="7" t="s">
+      <c r="A118" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="B118" s="3" t="s">
         <v>194</v>
       </c>
       <c r="C118" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="D118" s="7" t="s">
+      <c r="D118" s="3" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A119" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="B119" s="7" t="s">
+      <c r="A119" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="B119" s="3" t="s">
         <v>194</v>
       </c>
       <c r="C119" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="D119" s="7" t="s">
+      <c r="D119" s="3" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A120" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="B120" s="7" t="s">
+      <c r="A120" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="B120" s="3" t="s">
         <v>194</v>
       </c>
       <c r="C120" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="D120" s="7" t="s">
+      <c r="D120" s="3" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A121" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="B121" s="7" t="s">
-        <v>194</v>
+      <c r="A121" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B121" s="3" t="s">
+        <v>195</v>
       </c>
       <c r="C121" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="D121" s="7" t="s">
-        <v>179</v>
+      <c r="D121" s="3" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A122" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="B122" s="7" t="s">
-        <v>194</v>
+      <c r="A122" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B122" s="3" t="s">
+        <v>195</v>
       </c>
       <c r="C122" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="D122" s="7" t="s">
-        <v>179</v>
+      <c r="D122" s="3" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A123" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B123" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="B123" s="3" t="s">
         <v>195</v>
       </c>
       <c r="C123" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="D123" s="7" t="s">
+      <c r="D123" s="3" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A124" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B124" s="7" t="s">
-        <v>195</v>
+      <c r="A124" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B124" s="3" t="s">
+        <v>196</v>
       </c>
       <c r="C124" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="D124" s="7" t="s">
-        <v>177</v>
+      <c r="D124" s="3" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A125" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="B125" s="7" t="s">
-        <v>195</v>
+        <v>26</v>
+      </c>
+      <c r="B125" s="3" t="s">
+        <v>196</v>
       </c>
       <c r="C125" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="D125" s="7" t="s">
-        <v>177</v>
+      <c r="D125" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A126" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="B126" s="7" t="s">
-        <v>196</v>
+      <c r="A126" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B126" s="3" t="s">
+        <v>198</v>
       </c>
       <c r="C126" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="D126" s="7" t="s">
-        <v>182</v>
+      <c r="D126" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A127" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B127" s="7" t="s">
-        <v>196</v>
+        <v>50</v>
+      </c>
+      <c r="B127" s="3" t="s">
+        <v>198</v>
       </c>
       <c r="C127" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="D127" s="17" t="s">
-        <v>182</v>
+      <c r="D127" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A128" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B128" s="7" t="s">
-        <v>198</v>
+        <v>106</v>
+      </c>
+      <c r="B128" s="3" t="s">
+        <v>197</v>
       </c>
       <c r="C128" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="D128" s="17" t="s">
-        <v>185</v>
+      <c r="D128" s="3" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A129" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B129" s="7" t="s">
-        <v>198</v>
-      </c>
-      <c r="C129" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="D129" s="17" t="s">
-        <v>185</v>
+      <c r="A129" t="s">
+        <v>135</v>
+      </c>
+      <c r="B129" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="C129" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="D129" s="3" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A130" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="B130" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="C130" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="D130" s="7" t="s">
-        <v>187</v>
+      <c r="A130" t="s">
+        <v>145</v>
+      </c>
+      <c r="B130" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="C130" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="D130" s="3" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A131" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="B131" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="C131" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="D131" s="7" t="s">
-        <v>186</v>
+      <c r="A131" s="17" t="s">
+        <v>206</v>
+      </c>
+      <c r="B131" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C131" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="D131" s="3" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A132" s="11" t="s">
-        <v>145</v>
-      </c>
-      <c r="B132" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="C132" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="D132" s="7" t="s">
-        <v>186</v>
+      <c r="A132" s="17" t="s">
+        <v>209</v>
+      </c>
+      <c r="B132" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C132" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="D132" s="3" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A133" s="24" t="s">
-        <v>206</v>
-      </c>
-      <c r="B133" s="7" t="s">
+      <c r="A133" s="17" t="s">
+        <v>213</v>
+      </c>
+      <c r="B133" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="C133" s="9" t="s">
+      <c r="C133" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="D133" s="7" t="s">
+      <c r="D133" s="3" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A134" s="24" t="s">
-        <v>209</v>
-      </c>
-      <c r="B134" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="C134" s="9" t="s">
+      <c r="A134" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B134" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C134" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="D134" s="7" t="s">
-        <v>215</v>
+      <c r="D134" s="3" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A135" s="24" t="s">
-        <v>213</v>
-      </c>
-      <c r="B135" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="C135" s="9" t="s">
+      <c r="A135" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B135" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C135" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="D135" s="7" t="s">
-        <v>215</v>
+      <c r="D135" s="3" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A136" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B136" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="B136" s="3" t="s">
         <v>200</v>
       </c>
       <c r="C136" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="D136" s="7" t="s">
+      <c r="D136" s="3" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A137" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B137" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="B137" s="3" t="s">
         <v>200</v>
       </c>
       <c r="C137" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="D137" s="7" t="s">
+      <c r="D137" s="3" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A138" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="B138" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="B138" s="3" t="s">
         <v>200</v>
       </c>
       <c r="C138" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="D138" s="7" t="s">
+      <c r="D138" s="3" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A139" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="B139" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="B139" s="3" t="s">
         <v>200</v>
       </c>
       <c r="C139" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="D139" s="7" t="s">
+      <c r="D139" s="3" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A140" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B140" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="B140" s="3" t="s">
         <v>200</v>
       </c>
       <c r="C140" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="D140" s="7" t="s">
+      <c r="D140" s="3" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A141" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="B141" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="B141" s="3" t="s">
         <v>200</v>
       </c>
       <c r="C141" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="D141" s="7" t="s">
+      <c r="D141" s="3" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A142" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="B142" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="B142" s="3" t="s">
         <v>200</v>
       </c>
       <c r="C142" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="D142" s="7" t="s">
+      <c r="D142" s="3" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A143" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B143" s="7" t="s">
+      <c r="A143" t="s">
+        <v>158</v>
+      </c>
+      <c r="B143" s="3" t="s">
         <v>200</v>
       </c>
       <c r="C143" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="D143" s="7" t="s">
+      <c r="D143" s="3" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A144" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="B144" s="7" t="s">
+      <c r="A144" t="s">
+        <v>160</v>
+      </c>
+      <c r="B144" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="C144" s="10" t="s">
+      <c r="C144" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="D144" s="7" t="s">
+      <c r="D144" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="E144" s="9"/>
+      <c r="E144" s="7"/>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A145" s="11" t="s">
-        <v>158</v>
-      </c>
-      <c r="B145" s="7" t="s">
+      <c r="A145" t="s">
+        <v>161</v>
+      </c>
+      <c r="B145" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="C145" s="10" t="s">
+      <c r="C145" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="D145" s="7" t="s">
+      <c r="D145" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="E145" s="9"/>
+      <c r="E145" s="7"/>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A146" s="11" t="s">
-        <v>160</v>
-      </c>
-      <c r="B146" s="7" t="s">
+      <c r="A146" t="s">
+        <v>162</v>
+      </c>
+      <c r="B146" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="C146" s="10" t="s">
+      <c r="C146" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="D146" s="7" t="s">
+      <c r="D146" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="E146" s="9"/>
+      <c r="E146" s="7"/>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A147" s="11" t="s">
-        <v>161</v>
-      </c>
-      <c r="B147" s="7" t="s">
-        <v>200</v>
-      </c>
-      <c r="C147" s="10" t="s">
+      <c r="A147" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B147" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="C147" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="D147" s="7" t="s">
+      <c r="D147" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="E147" s="9"/>
+      <c r="E147" s="7"/>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A148" s="11" t="s">
-        <v>162</v>
-      </c>
-      <c r="B148" s="7" t="s">
-        <v>200</v>
-      </c>
-      <c r="C148" s="10" t="s">
+      <c r="A148" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B148" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="C148" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="D148" s="7" t="s">
+      <c r="D148" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="E148" s="9"/>
+      <c r="E148" s="7"/>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A149" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B149" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="B149" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="C149" s="10" t="s">
+      <c r="C149" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="D149" s="7" t="s">
+      <c r="D149" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="E149" s="9"/>
+      <c r="E149" s="7"/>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A150" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B150" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="C150" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B150" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="C150" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="D150" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="E150" s="9"/>
+      <c r="D150" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="E150" s="7"/>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A151" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="B151" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="C151" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="B151" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="C151" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="D151" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="E151" s="9"/>
+      <c r="D151" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="E151" s="7"/>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A152" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B152" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="C152" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B152" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="C152" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="D152" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="E152" s="9"/>
+      <c r="D152" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="E152" s="7"/>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A153" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="B153" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="C153" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="B153" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="C153" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="D153" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="E153" s="9"/>
+      <c r="D153" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="E153" s="7"/>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A154" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B154" s="7" t="s">
-        <v>192</v>
-      </c>
-      <c r="C154" s="10" t="s">
+      <c r="A154" t="s">
+        <v>18</v>
+      </c>
+      <c r="B154" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="C154" s="20" t="s">
         <v>172</v>
       </c>
-      <c r="D154" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="E154" s="9"/>
+      <c r="D154" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="E154" s="7"/>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A155" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="B155" s="7" t="s">
-        <v>192</v>
-      </c>
-      <c r="C155" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B155" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="C155" s="20" t="s">
         <v>172</v>
       </c>
-      <c r="D155" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="E155" s="9"/>
+      <c r="D155" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="E155" s="7"/>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A156" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="B156" s="7" t="s">
+      <c r="A156" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B156" s="3" t="s">
         <v>194</v>
       </c>
       <c r="C156" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="D156" s="7" t="s">
-        <v>179</v>
+      <c r="D156" s="3" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A157" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B157" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="B157" s="3" t="s">
         <v>194</v>
       </c>
       <c r="C157" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="D157" s="7" t="s">
+      <c r="D157" s="3" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A158" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B158" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="B158" s="3" t="s">
         <v>194</v>
       </c>
       <c r="C158" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="D158" s="7" t="s">
+      <c r="D158" s="3" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A159" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="B159" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="B159" s="3" t="s">
         <v>194</v>
       </c>
       <c r="C159" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="D159" s="7" t="s">
+      <c r="D159" s="3" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A160" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="B160" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="B160" s="3" t="s">
         <v>194</v>
       </c>
       <c r="C160" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="D160" s="7" t="s">
+      <c r="D160" s="3" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A161" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="B161" s="7" t="s">
-        <v>194</v>
+        <v>2</v>
+      </c>
+      <c r="B161" s="3" t="s">
+        <v>195</v>
       </c>
       <c r="C161" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="D161" s="7" t="s">
-        <v>178</v>
+      <c r="D161" s="3" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A162" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="B162" s="7" t="s">
-        <v>194</v>
+        <v>67</v>
+      </c>
+      <c r="B162" s="3" t="s">
+        <v>195</v>
       </c>
       <c r="C162" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="D162" s="7" t="s">
-        <v>178</v>
+      <c r="D162" s="3" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A163" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B163" s="7" t="s">
-        <v>195</v>
+      <c r="A163" t="s">
+        <v>15</v>
+      </c>
+      <c r="B163" s="3" t="s">
+        <v>196</v>
       </c>
       <c r="C163" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="D163" s="7" t="s">
-        <v>177</v>
+      <c r="D163" s="3" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A164" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B164" s="7" t="s">
-        <v>195</v>
+      <c r="A164" t="s">
+        <v>16</v>
+      </c>
+      <c r="B164" s="3" t="s">
+        <v>196</v>
       </c>
       <c r="C164" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="D164" s="7" t="s">
-        <v>177</v>
+      <c r="D164" s="3" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A165" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B165" s="7" t="s">
+      <c r="A165" t="s">
+        <v>19</v>
+      </c>
+      <c r="B165" s="3" t="s">
         <v>196</v>
       </c>
       <c r="C165" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="D165" s="7" t="s">
+      <c r="D165" s="3" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A166" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="B166" s="7" t="s">
+      <c r="A166" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B166" s="3" t="s">
         <v>196</v>
       </c>
       <c r="C166" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="D166" s="7" t="s">
+      <c r="D166" s="3" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A167" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="B167" s="7" t="s">
+      <c r="A167" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B167" s="3" t="s">
         <v>196</v>
       </c>
       <c r="C167" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="D167" s="7" t="s">
+      <c r="D167" s="3" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A168" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B168" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B168" s="3" t="s">
         <v>196</v>
       </c>
       <c r="C168" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="D168" s="7" t="s">
+      <c r="D168" s="3" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A169" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B169" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B169" s="3" t="s">
         <v>196</v>
       </c>
       <c r="C169" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="D169" s="7" t="s">
+      <c r="D169" s="3" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A170" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B170" s="7" t="s">
-        <v>196</v>
+      <c r="A170" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="B170" s="3" t="s">
+        <v>198</v>
       </c>
       <c r="C170" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="D170" s="7" t="s">
-        <v>182</v>
+      <c r="D170" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A171" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B171" s="7" t="s">
-        <v>196</v>
-      </c>
-      <c r="C171" s="10" t="s">
+      <c r="A171" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="B171" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="C171" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="D171" s="7" t="s">
-        <v>182</v>
+      <c r="D171" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A172" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B172" s="7" t="s">
+      <c r="A172" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="B172" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="C172" s="10" t="s">
+      <c r="C172" s="20" t="s">
         <v>172</v>
       </c>
-      <c r="D172" s="17" t="s">
+      <c r="D172" t="s">
         <v>185</v>
       </c>
     </row>
@@ -5520,97 +5184,97 @@
       <c r="A173" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="B173" s="7" t="s">
+      <c r="B173" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="C173" s="10" t="s">
+      <c r="C173" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="D173" s="7" t="s">
+      <c r="D173" s="3" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A174" s="8" t="s">
+      <c r="A174" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="B174" s="7" t="s">
+      <c r="B174" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="C174" s="12" t="s">
+      <c r="C174" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="D174" s="7" t="s">
+      <c r="D174" s="3" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A175" s="8" t="s">
+      <c r="A175" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="B175" s="7" t="s">
+      <c r="B175" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="C175" s="12" t="s">
+      <c r="C175" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="D175" s="7" t="s">
+      <c r="D175" s="3" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A176" s="8" t="s">
+      <c r="A176" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="B176" s="7" t="s">
+      <c r="B176" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="C176" s="12" t="s">
+      <c r="C176" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="D176" s="7" t="s">
+      <c r="D176" s="3" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A177" s="8" t="s">
+      <c r="A177" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="B177" s="7" t="s">
+      <c r="B177" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="C177" s="12" t="s">
+      <c r="C177" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="D177" s="7" t="s">
+      <c r="D177" s="3" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A178" s="8" t="s">
+      <c r="A178" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="B178" s="7" t="s">
+      <c r="B178" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="C178" s="12" t="s">
+      <c r="C178" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="D178" s="7" t="s">
+      <c r="D178" s="3" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A179" s="8" t="s">
+      <c r="A179" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="B179" s="7" t="s">
+      <c r="B179" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="C179" s="12" t="s">
+      <c r="C179" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="D179" s="7" t="s">
+      <c r="D179" s="3" t="s">
         <v>186</v>
       </c>
     </row>
@@ -5621,7 +5285,7 @@
     <sortCondition ref="A2:A179"/>
   </sortState>
   <hyperlinks>
-    <hyperlink ref="D87" r:id="rId1" xr:uid="{0E5A7D6F-CF2D-4F80-A7D0-43969497342C}"/>
+    <hyperlink ref="D85" r:id="rId1" xr:uid="{0E5A7D6F-CF2D-4F80-A7D0-43969497342C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
